--- a/research/traditional_assets/database/data/kenya/kenya_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_retail_automotive.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1477375342772466</v>
+        <v>0.1473258216744148</v>
       </c>
       <c r="C2">
-        <v>92.81640217724392</v>
+        <v>92.3626219495095</v>
       </c>
       <c r="D2">
-        <v>91.04640217724392</v>
+        <v>91.4156181126645</v>
       </c>
       <c r="E2">
-        <v>-68.19961631550026</v>
+        <v>-67.37662015234527</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8229961631550026</v>
       </c>
       <c r="G2">
         <v>1.77</v>
@@ -1433,28 +1433,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04139670700669663</v>
       </c>
       <c r="N2">
-        <v>13.30333333333333</v>
+        <v>13.26193662632664</v>
       </c>
       <c r="O2">
-        <v>3.991</v>
+        <v>3.978580987897991</v>
       </c>
       <c r="P2">
-        <v>9.312333333333335</v>
+        <v>9.283355638428645</v>
       </c>
       <c r="Q2">
-        <v>9.442333333333336</v>
+        <v>9.413355638428646</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1477375342772466</v>
+        <v>0.1484583047216312</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307609</v>
+        <v>0.7157791324494631</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>321.3621153774693</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1473258216744148</v>
+        <v>0.1469141090715831</v>
       </c>
       <c r="C3">
-        <v>92.3626219495095</v>
+        <v>91.91184844072205</v>
       </c>
       <c r="D3">
-        <v>91.4156181126645</v>
+        <v>91.78784076703207</v>
       </c>
       <c r="E3">
-        <v>-67.37662015234527</v>
+        <v>-66.55362398919026</v>
       </c>
       <c r="F3">
-        <v>0.8229961631550026</v>
+        <v>1.645992326310005</v>
       </c>
       <c r="G3">
         <v>1.77</v>
@@ -1515,28 +1515,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M3">
-        <v>0.04139670700669663</v>
+        <v>0.08279341401339325</v>
       </c>
       <c r="N3">
-        <v>13.26193662632664</v>
+        <v>13.22053991931994</v>
       </c>
       <c r="O3">
-        <v>3.978580987897991</v>
+        <v>3.966161975795982</v>
       </c>
       <c r="P3">
-        <v>9.283355638428645</v>
+        <v>9.254377943523959</v>
       </c>
       <c r="Q3">
-        <v>9.413355638428646</v>
+        <v>9.38437794352396</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1484583047216312</v>
+        <v>0.1491937847669216</v>
       </c>
       <c r="T3">
-        <v>0.7157791324494631</v>
+        <v>0.720907224815486</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>321.3621153774693</v>
+        <v>160.6810576887347</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1469141090715831</v>
+        <v>0.1465023964687514</v>
       </c>
       <c r="C4">
-        <v>91.91184844072205</v>
+        <v>91.46411852897376</v>
       </c>
       <c r="D4">
-        <v>91.78784076703207</v>
+        <v>92.16310701843877</v>
       </c>
       <c r="E4">
-        <v>-66.55362398919026</v>
+        <v>-65.73062782603526</v>
       </c>
       <c r="F4">
-        <v>1.645992326310005</v>
+        <v>2.468988489465008</v>
       </c>
       <c r="G4">
         <v>1.77</v>
@@ -1597,28 +1597,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M4">
-        <v>0.08279341401339325</v>
+        <v>0.1241901210200899</v>
       </c>
       <c r="N4">
-        <v>13.22053991931994</v>
+        <v>13.17914321231324</v>
       </c>
       <c r="O4">
-        <v>3.966161975795982</v>
+        <v>3.953742963693973</v>
       </c>
       <c r="P4">
-        <v>9.254377943523959</v>
+        <v>9.225400248619271</v>
       </c>
       <c r="Q4">
-        <v>9.38437794352396</v>
+        <v>9.355400248619272</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1491937847669216</v>
+        <v>0.1499444293492282</v>
       </c>
       <c r="T4">
-        <v>0.720907224815486</v>
+        <v>0.7261410510447257</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>160.6810576887347</v>
+        <v>107.1207051258231</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1465023964687514</v>
+        <v>0.1460906838659196</v>
       </c>
       <c r="C5">
-        <v>91.46411852897376</v>
+        <v>91.0194696979234</v>
       </c>
       <c r="D5">
-        <v>92.16310701843877</v>
+        <v>92.54145435054342</v>
       </c>
       <c r="E5">
-        <v>-65.73062782603526</v>
+        <v>-64.90763166288025</v>
       </c>
       <c r="F5">
-        <v>2.468988489465008</v>
+        <v>3.29198465262001</v>
       </c>
       <c r="G5">
         <v>1.77</v>
@@ -1679,28 +1679,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M5">
-        <v>0.1241901210200899</v>
+        <v>0.1655868280267865</v>
       </c>
       <c r="N5">
-        <v>13.17914321231324</v>
+        <v>13.13774650530655</v>
       </c>
       <c r="O5">
-        <v>3.953742963693973</v>
+        <v>3.941323951591964</v>
       </c>
       <c r="P5">
-        <v>9.225400248619271</v>
+        <v>9.196422553714584</v>
       </c>
       <c r="Q5">
-        <v>9.355400248619272</v>
+        <v>9.326422553714584</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1499444293492282</v>
+        <v>0.150710712360333</v>
       </c>
       <c r="T5">
-        <v>0.7261410510447257</v>
+        <v>0.731483915320408</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>107.1207051258231</v>
+        <v>80.34052884436734</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1460906838659196</v>
+        <v>0.1456789712630879</v>
       </c>
       <c r="C6">
-        <v>91.0194696979234</v>
+        <v>90.57794004927761</v>
       </c>
       <c r="D6">
-        <v>92.54145435054342</v>
+        <v>92.92292086505263</v>
       </c>
       <c r="E6">
-        <v>-64.90763166288025</v>
+        <v>-64.08463549972525</v>
       </c>
       <c r="F6">
-        <v>3.29198465262001</v>
+        <v>4.114980815775013</v>
       </c>
       <c r="G6">
         <v>1.77</v>
@@ -1761,28 +1761,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M6">
-        <v>0.1655868280267865</v>
+        <v>0.2069835350334831</v>
       </c>
       <c r="N6">
-        <v>13.13774650530655</v>
+        <v>13.09634979829985</v>
       </c>
       <c r="O6">
-        <v>3.941323951591964</v>
+        <v>3.928904939489955</v>
       </c>
       <c r="P6">
-        <v>9.196422553714584</v>
+        <v>9.167444858809896</v>
       </c>
       <c r="Q6">
-        <v>9.326422553714584</v>
+        <v>9.297444858809897</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.150710712360333</v>
+        <v>0.1514931276453557</v>
       </c>
       <c r="T6">
-        <v>0.731483915320408</v>
+        <v>0.7369392609492625</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>80.34052884436734</v>
+        <v>64.27242307549386</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1456789712630879</v>
+        <v>0.1452672586602561</v>
       </c>
       <c r="C7">
-        <v>90.57794004927761</v>
+        <v>90.13956831558193</v>
       </c>
       <c r="D7">
-        <v>92.92292086505263</v>
+        <v>93.30754529451194</v>
       </c>
       <c r="E7">
-        <v>-64.08463549972525</v>
+        <v>-63.26163933657025</v>
       </c>
       <c r="F7">
-        <v>4.114980815775013</v>
+        <v>4.937976978930016</v>
       </c>
       <c r="G7">
         <v>1.77</v>
@@ -1843,28 +1843,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M7">
-        <v>0.2069835350334831</v>
+        <v>0.2483802420401798</v>
       </c>
       <c r="N7">
-        <v>13.09634979829985</v>
+        <v>13.05495309129316</v>
       </c>
       <c r="O7">
-        <v>3.928904939489955</v>
+        <v>3.916485927387947</v>
       </c>
       <c r="P7">
-        <v>9.167444858809896</v>
+        <v>9.138467163905208</v>
       </c>
       <c r="Q7">
-        <v>9.297444858809897</v>
+        <v>9.268467163905209</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1514931276453557</v>
+        <v>0.1522921900641023</v>
       </c>
       <c r="T7">
-        <v>0.7369392609492625</v>
+        <v>0.7425106777617096</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>64.27242307549386</v>
+        <v>53.56035256291155</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1452672586602561</v>
+        <v>0.1448555460574244</v>
       </c>
       <c r="C8">
-        <v>90.13956831558193</v>
+        <v>89.70439387333056</v>
       </c>
       <c r="D8">
-        <v>93.30754529451194</v>
+        <v>93.69536701541558</v>
       </c>
       <c r="E8">
-        <v>-63.26163933657025</v>
+        <v>-62.43864317341524</v>
       </c>
       <c r="F8">
-        <v>4.937976978930015</v>
+        <v>5.760973142085017</v>
       </c>
       <c r="G8">
         <v>1.77</v>
@@ -1925,28 +1925,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M8">
-        <v>0.2483802420401797</v>
+        <v>0.2897769490468763</v>
       </c>
       <c r="N8">
-        <v>13.05495309129316</v>
+        <v>13.01355638428646</v>
       </c>
       <c r="O8">
-        <v>3.916485927387947</v>
+        <v>3.904066915285937</v>
       </c>
       <c r="P8">
-        <v>9.138467163905208</v>
+        <v>9.109489469000522</v>
       </c>
       <c r="Q8">
-        <v>9.268467163905209</v>
+        <v>9.239489469000523</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1522921900641023</v>
+        <v>0.1531084366208865</v>
       </c>
       <c r="T8">
-        <v>0.7425106777617096</v>
+        <v>0.7482019099894784</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>53.56035256291156</v>
+        <v>45.90887362535277</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1448555460574245</v>
+        <v>0.1444438334545927</v>
       </c>
       <c r="C9">
-        <v>89.70439387333053</v>
+        <v>89.27245675640521</v>
       </c>
       <c r="D9">
-        <v>93.69536701541556</v>
+        <v>94.08642606164523</v>
       </c>
       <c r="E9">
-        <v>-62.43864317341524</v>
+        <v>-61.61564701026025</v>
       </c>
       <c r="F9">
-        <v>5.760973142085018</v>
+        <v>6.583969305240021</v>
       </c>
       <c r="G9">
         <v>1.77</v>
@@ -2007,28 +2007,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M9">
-        <v>0.2897769490468764</v>
+        <v>0.331173656053573</v>
       </c>
       <c r="N9">
-        <v>13.01355638428646</v>
+        <v>12.97215967727976</v>
       </c>
       <c r="O9">
-        <v>3.904066915285937</v>
+        <v>3.891647903183928</v>
       </c>
       <c r="P9">
-        <v>9.109489469000522</v>
+        <v>9.080511774095832</v>
       </c>
       <c r="Q9">
-        <v>9.239489469000523</v>
+        <v>9.210511774095833</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1531084366208865</v>
+        <v>0.1539424276680355</v>
       </c>
       <c r="T9">
-        <v>0.7482019099894784</v>
+        <v>0.7540168646569811</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.90887362535276</v>
+        <v>40.17026442218366</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1444438334545927</v>
+        <v>0.1440321208517609</v>
       </c>
       <c r="C10">
-        <v>89.27245675640521</v>
+        <v>88.843797669851</v>
       </c>
       <c r="D10">
-        <v>94.08642606164523</v>
+        <v>94.48076313824603</v>
       </c>
       <c r="E10">
-        <v>-61.61564701026025</v>
+        <v>-60.79265084710524</v>
       </c>
       <c r="F10">
-        <v>6.583969305240021</v>
+        <v>7.406965468395023</v>
       </c>
       <c r="G10">
         <v>1.77</v>
@@ -2089,28 +2089,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M10">
-        <v>0.331173656053573</v>
+        <v>0.3725703630602696</v>
       </c>
       <c r="N10">
-        <v>12.97215967727976</v>
+        <v>12.93076297027307</v>
       </c>
       <c r="O10">
-        <v>3.891647903183928</v>
+        <v>3.879228891081919</v>
       </c>
       <c r="P10">
-        <v>9.080511774095832</v>
+        <v>9.051534079191146</v>
       </c>
       <c r="Q10">
-        <v>9.210511774095833</v>
+        <v>9.181534079191147</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1539424276680355</v>
+        <v>0.1547947481887483</v>
       </c>
       <c r="T10">
-        <v>0.7540168646569811</v>
+        <v>0.7599596205259673</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.17026442218366</v>
+        <v>35.7069017086077</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1440321208517609</v>
+        <v>0.1436204082489292</v>
       </c>
       <c r="C11">
-        <v>88.843797669851</v>
+        <v>88.41845800400058</v>
       </c>
       <c r="D11">
-        <v>94.48076313824603</v>
+        <v>94.87841963555061</v>
       </c>
       <c r="E11">
-        <v>-60.79265084710524</v>
+        <v>-59.96965468395024</v>
       </c>
       <c r="F11">
-        <v>7.406965468395023</v>
+        <v>8.229961631550026</v>
       </c>
       <c r="G11">
         <v>1.77</v>
@@ -2171,28 +2171,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M11">
-        <v>0.3725703630602696</v>
+        <v>0.4139670700669663</v>
       </c>
       <c r="N11">
-        <v>12.93076297027307</v>
+        <v>12.88936626326637</v>
       </c>
       <c r="O11">
-        <v>3.879228891081919</v>
+        <v>3.86680987897991</v>
       </c>
       <c r="P11">
-        <v>9.051534079191146</v>
+        <v>9.022556384286457</v>
       </c>
       <c r="Q11">
-        <v>9.181534079191147</v>
+        <v>9.152556384286457</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1547947481887483</v>
+        <v>0.1556660091654769</v>
       </c>
       <c r="T11">
-        <v>0.7599596205259673</v>
+        <v>0.7660344376364867</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.7069017086077</v>
+        <v>32.13621153774693</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1436204082489292</v>
+        <v>0.1432086956460975</v>
       </c>
       <c r="C12">
-        <v>88.41845800400058</v>
+        <v>87.99647984895685</v>
       </c>
       <c r="D12">
-        <v>94.87841963555061</v>
+        <v>95.27943764366188</v>
       </c>
       <c r="E12">
-        <v>-59.96965468395024</v>
+        <v>-59.14665852079523</v>
       </c>
       <c r="F12">
-        <v>8.229961631550026</v>
+        <v>9.052957794705028</v>
       </c>
       <c r="G12">
         <v>1.77</v>
@@ -2253,28 +2253,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M12">
-        <v>0.4139670700669663</v>
+        <v>0.4553637770736629</v>
       </c>
       <c r="N12">
-        <v>12.88936626326637</v>
+        <v>12.84796955625967</v>
       </c>
       <c r="O12">
-        <v>3.86680987897991</v>
+        <v>3.854390866877901</v>
       </c>
       <c r="P12">
-        <v>9.022556384286457</v>
+        <v>8.993578689381771</v>
       </c>
       <c r="Q12">
-        <v>9.152556384286457</v>
+        <v>9.123578689381771</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1556660091654769</v>
+        <v>0.156556849040559</v>
       </c>
       <c r="T12">
-        <v>0.7660344376364867</v>
+        <v>0.7722457674910627</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.13621153774693</v>
+        <v>29.21473776158812</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1432086956460975</v>
+        <v>0.1427969830432657</v>
       </c>
       <c r="C13">
-        <v>87.99647984895685</v>
+        <v>87.57790600944381</v>
       </c>
       <c r="D13">
-        <v>95.27943764366188</v>
+        <v>95.68385996730385</v>
       </c>
       <c r="E13">
-        <v>-59.14665852079523</v>
+        <v>-58.32366235764023</v>
       </c>
       <c r="F13">
-        <v>9.052957794705028</v>
+        <v>9.87595395786003</v>
       </c>
       <c r="G13">
         <v>1.77</v>
@@ -2335,28 +2335,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M13">
-        <v>0.4553637770736629</v>
+        <v>0.4967604840803595</v>
       </c>
       <c r="N13">
-        <v>12.84796955625967</v>
+        <v>12.80657284925297</v>
       </c>
       <c r="O13">
-        <v>3.854390866877901</v>
+        <v>3.841971854775892</v>
       </c>
       <c r="P13">
-        <v>8.993578689381771</v>
+        <v>8.964600994477083</v>
       </c>
       <c r="Q13">
-        <v>9.123578689381771</v>
+        <v>9.094600994477084</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.156556849040559</v>
+        <v>0.1574679352764383</v>
       </c>
       <c r="T13">
-        <v>0.7722457674910627</v>
+        <v>0.7785982639332426</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.21473776158812</v>
+        <v>26.78017628145578</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1427969830432657</v>
+        <v>0.142385270440434</v>
       </c>
       <c r="C14">
-        <v>87.57790600944381</v>
+        <v>87.16278002003772</v>
       </c>
       <c r="D14">
-        <v>95.68385996730385</v>
+        <v>96.09173014105275</v>
       </c>
       <c r="E14">
-        <v>-58.32366235764023</v>
+        <v>-57.50066619448523</v>
       </c>
       <c r="F14">
-        <v>9.87595395786003</v>
+        <v>10.69895012101503</v>
       </c>
       <c r="G14">
         <v>1.77</v>
@@ -2417,28 +2417,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M14">
-        <v>0.4967604840803595</v>
+        <v>0.5381571910870562</v>
       </c>
       <c r="N14">
-        <v>12.80657284925297</v>
+        <v>12.76517614224628</v>
       </c>
       <c r="O14">
-        <v>3.841971854775892</v>
+        <v>3.829552842673884</v>
       </c>
       <c r="P14">
-        <v>8.964600994477083</v>
+        <v>8.935623299572395</v>
       </c>
       <c r="Q14">
-        <v>9.094600994477084</v>
+        <v>9.065623299572396</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1574679352764383</v>
+        <v>0.1583999660234874</v>
       </c>
       <c r="T14">
-        <v>0.7785982639332426</v>
+        <v>0.7850967947763922</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.78017628145578</v>
+        <v>24.72016272134379</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.142385270440434</v>
+        <v>0.1419735578376022</v>
       </c>
       <c r="C15">
-        <v>87.16278002003772</v>
+        <v>86.75114616078942</v>
       </c>
       <c r="D15">
-        <v>96.09173014105275</v>
+        <v>96.50309244495946</v>
       </c>
       <c r="E15">
-        <v>-57.50066619448523</v>
+        <v>-56.67767003133023</v>
       </c>
       <c r="F15">
-        <v>10.69895012101503</v>
+        <v>11.52194628417004</v>
       </c>
       <c r="G15">
         <v>1.77</v>
@@ -2499,28 +2499,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M15">
-        <v>0.5381571910870562</v>
+        <v>0.5795538980937528</v>
       </c>
       <c r="N15">
-        <v>12.76517614224628</v>
+        <v>12.72377943523958</v>
       </c>
       <c r="O15">
-        <v>3.829552842673884</v>
+        <v>3.817133830571874</v>
       </c>
       <c r="P15">
-        <v>8.935623299572395</v>
+        <v>8.906645604667707</v>
       </c>
       <c r="Q15">
-        <v>9.065623299572396</v>
+        <v>9.036645604667708</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1583999660234874</v>
+        <v>0.1593536719041886</v>
       </c>
       <c r="T15">
-        <v>0.7850967947763922</v>
+        <v>0.791746454243801</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.72016272134379</v>
+        <v>22.95443681267638</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1419735578376022</v>
+        <v>0.1415618452347705</v>
       </c>
       <c r="C16">
-        <v>86.75114616078942</v>
+        <v>86.34304947324937</v>
       </c>
       <c r="D16">
-        <v>96.50309244495946</v>
+        <v>96.91799192057441</v>
       </c>
       <c r="E16">
-        <v>-56.67767003133023</v>
+        <v>-55.85467386817523</v>
       </c>
       <c r="F16">
-        <v>11.52194628417004</v>
+        <v>12.34494244732504</v>
       </c>
       <c r="G16">
         <v>1.77</v>
@@ -2581,28 +2581,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M16">
-        <v>0.5795538980937528</v>
+        <v>0.6209506051004495</v>
       </c>
       <c r="N16">
-        <v>12.72377943523958</v>
+        <v>12.68238272823288</v>
       </c>
       <c r="O16">
-        <v>3.817133830571874</v>
+        <v>3.804714818469865</v>
       </c>
       <c r="P16">
-        <v>8.906645604667707</v>
+        <v>8.877667909763019</v>
       </c>
       <c r="Q16">
-        <v>9.036645604667708</v>
+        <v>9.00766790976302</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1593536719041886</v>
+        <v>0.1603298179232594</v>
       </c>
       <c r="T16">
-        <v>0.791746454243801</v>
+        <v>0.7985525762869137</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.95443681267638</v>
+        <v>21.42414102516462</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1415618452347705</v>
+        <v>0.1411501326319387</v>
       </c>
       <c r="C17">
-        <v>86.34304947324937</v>
+        <v>85.93853577690828</v>
       </c>
       <c r="D17">
-        <v>96.91799192057441</v>
+        <v>97.33647438738832</v>
       </c>
       <c r="E17">
-        <v>-55.85467386817523</v>
+        <v>-55.03167770502022</v>
       </c>
       <c r="F17">
-        <v>12.34494244732504</v>
+        <v>13.16793861048004</v>
       </c>
       <c r="G17">
         <v>1.77</v>
@@ -2663,28 +2663,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M17">
-        <v>0.6209506051004494</v>
+        <v>0.662347312107146</v>
       </c>
       <c r="N17">
-        <v>12.68238272823288</v>
+        <v>12.64098602122619</v>
       </c>
       <c r="O17">
-        <v>3.804714818469865</v>
+        <v>3.792295806367856</v>
       </c>
       <c r="P17">
-        <v>8.877667909763019</v>
+        <v>8.848690214858333</v>
       </c>
       <c r="Q17">
-        <v>9.00766790976302</v>
+        <v>8.978690214858334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1603298179232594</v>
+        <v>0.1613292055142128</v>
       </c>
       <c r="T17">
-        <v>0.7985525762869137</v>
+        <v>0.8055207488548622</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.42414102516462</v>
+        <v>20.08513221109183</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1411501326319387</v>
+        <v>0.1407384200291071</v>
       </c>
       <c r="C18">
-        <v>85.93853577690828</v>
+        <v>85.53765168606503</v>
       </c>
       <c r="D18">
-        <v>97.33647438738832</v>
+        <v>97.75858645970008</v>
       </c>
       <c r="E18">
-        <v>-55.03167770502022</v>
+        <v>-54.20868154186522</v>
       </c>
       <c r="F18">
-        <v>13.16793861048004</v>
+        <v>13.99093477363505</v>
       </c>
       <c r="G18">
         <v>1.77</v>
@@ -2745,28 +2745,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M18">
-        <v>0.662347312107146</v>
+        <v>0.7037440191138428</v>
       </c>
       <c r="N18">
-        <v>12.64098602122619</v>
+        <v>12.59958931421949</v>
       </c>
       <c r="O18">
-        <v>3.792295806367856</v>
+        <v>3.779876794265847</v>
       </c>
       <c r="P18">
-        <v>8.848690214858333</v>
+        <v>8.819712519953644</v>
       </c>
       <c r="Q18">
-        <v>8.978690214858334</v>
+        <v>8.949712519953644</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1613292055142128</v>
+        <v>0.1623526747338639</v>
       </c>
       <c r="T18">
-        <v>0.8055207488548622</v>
+        <v>0.8126568291955327</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.08513221109183</v>
+        <v>18.90365384573349</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1407384200291071</v>
+        <v>0.1403267074262753</v>
       </c>
       <c r="C19">
-        <v>85.53765168606503</v>
+        <v>85.14044462713613</v>
       </c>
       <c r="D19">
-        <v>97.75858645970008</v>
+        <v>98.18437556392618</v>
       </c>
       <c r="E19">
-        <v>-54.20868154186522</v>
+        <v>-53.38568537871021</v>
       </c>
       <c r="F19">
-        <v>13.99093477363505</v>
+        <v>14.81393093679005</v>
       </c>
       <c r="G19">
         <v>1.77</v>
@@ -2827,28 +2827,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M19">
-        <v>0.7037440191138428</v>
+        <v>0.7451407261205394</v>
       </c>
       <c r="N19">
-        <v>12.59958931421949</v>
+        <v>12.5581926072128</v>
       </c>
       <c r="O19">
-        <v>3.779876794265847</v>
+        <v>3.767457782163838</v>
       </c>
       <c r="P19">
-        <v>8.819712519953644</v>
+        <v>8.790734825048958</v>
       </c>
       <c r="Q19">
-        <v>8.949712519953644</v>
+        <v>8.920734825048958</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1623526747338639</v>
+        <v>0.1634011066174089</v>
       </c>
       <c r="T19">
-        <v>0.8126568291955327</v>
+        <v>0.8199669602762192</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.90365384573349</v>
+        <v>17.85345085430385</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1403267074262753</v>
+        <v>0.1399149948234436</v>
       </c>
       <c r="C20">
-        <v>85.14044462713612</v>
+        <v>84.74696285641845</v>
       </c>
       <c r="D20">
-        <v>98.18437556392617</v>
+        <v>98.61388995636351</v>
       </c>
       <c r="E20">
-        <v>-53.38568537871022</v>
+        <v>-52.56268921555522</v>
       </c>
       <c r="F20">
-        <v>14.81393093679005</v>
+        <v>15.63692709994505</v>
       </c>
       <c r="G20">
         <v>1.77</v>
@@ -2909,28 +2909,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M20">
-        <v>0.7451407261205393</v>
+        <v>0.786537433127236</v>
       </c>
       <c r="N20">
-        <v>12.5581926072128</v>
+        <v>12.5167959002061</v>
       </c>
       <c r="O20">
-        <v>3.767457782163838</v>
+        <v>3.755038770061829</v>
       </c>
       <c r="P20">
-        <v>8.790734825048958</v>
+        <v>8.761757130144268</v>
       </c>
       <c r="Q20">
-        <v>8.920734825048958</v>
+        <v>8.891757130144269</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1634011066174089</v>
+        <v>0.164475425707955</v>
       </c>
       <c r="T20">
-        <v>0.8199669602762192</v>
+        <v>0.8274575884206264</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.85345085430385</v>
+        <v>16.91379554618259</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1399149948234436</v>
+        <v>0.1395032822206118</v>
       </c>
       <c r="C21">
-        <v>84.74696285641845</v>
+        <v>84.35725547832125</v>
       </c>
       <c r="D21">
-        <v>98.61388995636351</v>
+        <v>99.04717874142131</v>
       </c>
       <c r="E21">
-        <v>-52.56268921555522</v>
+        <v>-51.73969305240021</v>
       </c>
       <c r="F21">
-        <v>15.63692709994505</v>
+        <v>16.45992326310005</v>
       </c>
       <c r="G21">
         <v>1.77</v>
@@ -2991,28 +2991,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M21">
-        <v>0.786537433127236</v>
+        <v>0.8279341401339325</v>
       </c>
       <c r="N21">
-        <v>12.5167959002061</v>
+        <v>12.4753991931994</v>
       </c>
       <c r="O21">
-        <v>3.755038770061829</v>
+        <v>3.742619757959821</v>
       </c>
       <c r="P21">
-        <v>8.761757130144268</v>
+        <v>8.732779435239582</v>
       </c>
       <c r="Q21">
-        <v>8.891757130144269</v>
+        <v>8.862779435239583</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.164475425707955</v>
+        <v>0.1655766027757648</v>
       </c>
       <c r="T21">
-        <v>0.8274575884206264</v>
+        <v>0.8351354822686441</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.91379554618259</v>
+        <v>16.06810576887347</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1395032822206118</v>
+        <v>0.1390915696177801</v>
       </c>
       <c r="C22">
-        <v>84.35725547832125</v>
+        <v>83.97137246408039</v>
       </c>
       <c r="D22">
-        <v>99.04717874142131</v>
+        <v>99.48429189033544</v>
       </c>
       <c r="E22">
-        <v>-51.73969305240021</v>
+        <v>-50.91669688924521</v>
       </c>
       <c r="F22">
-        <v>16.45992326310005</v>
+        <v>17.28291942625506</v>
       </c>
       <c r="G22">
         <v>1.77</v>
@@ -3073,28 +3073,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M22">
-        <v>0.8279341401339325</v>
+        <v>0.8693308471406292</v>
       </c>
       <c r="N22">
-        <v>12.4753991931994</v>
+        <v>12.43400248619271</v>
       </c>
       <c r="O22">
-        <v>3.742619757959821</v>
+        <v>3.730200745857811</v>
       </c>
       <c r="P22">
-        <v>8.732779435239582</v>
+        <v>8.703801740334894</v>
       </c>
       <c r="Q22">
-        <v>8.862779435239583</v>
+        <v>8.833801740334895</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1655766027757648</v>
+        <v>0.1667056577440254</v>
       </c>
       <c r="T22">
-        <v>0.8351354822686441</v>
+        <v>0.8430077531761051</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.06810576887347</v>
+        <v>15.30295787511759</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1390915696177801</v>
+        <v>0.1386798570149483</v>
       </c>
       <c r="C23">
-        <v>83.97137246408039</v>
+        <v>83.58936467097048</v>
       </c>
       <c r="D23">
-        <v>99.48429189033544</v>
+        <v>99.92528026038055</v>
       </c>
       <c r="E23">
-        <v>-50.91669688924522</v>
+        <v>-50.0937007260902</v>
       </c>
       <c r="F23">
-        <v>17.28291942625505</v>
+        <v>18.10591558941006</v>
       </c>
       <c r="G23">
         <v>1.77</v>
@@ -3155,28 +3155,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M23">
-        <v>0.8693308471406291</v>
+        <v>0.9107275541473258</v>
       </c>
       <c r="N23">
-        <v>12.43400248619271</v>
+        <v>12.39260577918601</v>
       </c>
       <c r="O23">
-        <v>3.730200745857811</v>
+        <v>3.717781733755803</v>
       </c>
       <c r="P23">
-        <v>8.703801740334894</v>
+        <v>8.674824045430206</v>
       </c>
       <c r="Q23">
-        <v>8.833801740334895</v>
+        <v>8.804824045430207</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1667056577440254</v>
+        <v>0.1678636628396774</v>
       </c>
       <c r="T23">
-        <v>0.8430077531761049</v>
+        <v>0.8510818771837573</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.30295787511759</v>
+        <v>14.60736888079406</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1386798570149483</v>
+        <v>0.1382681444121166</v>
       </c>
       <c r="C24">
-        <v>83.58936467097048</v>
+        <v>83.21128386203017</v>
       </c>
       <c r="D24">
-        <v>99.92528026038055</v>
+        <v>100.3701956145952</v>
       </c>
       <c r="E24">
-        <v>-50.0937007260902</v>
+        <v>-49.27070456293521</v>
       </c>
       <c r="F24">
-        <v>18.10591558941006</v>
+        <v>18.92891175256506</v>
       </c>
       <c r="G24">
         <v>1.77</v>
@@ -3237,28 +3237,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M24">
-        <v>0.9107275541473258</v>
+        <v>0.9521242611540225</v>
       </c>
       <c r="N24">
-        <v>12.39260577918601</v>
+        <v>12.35120907217931</v>
       </c>
       <c r="O24">
-        <v>3.717781733755803</v>
+        <v>3.705362721653794</v>
       </c>
       <c r="P24">
-        <v>8.674824045430206</v>
+        <v>8.645846350525519</v>
       </c>
       <c r="Q24">
-        <v>8.804824045430207</v>
+        <v>8.775846350525519</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1678636628396774</v>
+        <v>0.1690517459897618</v>
       </c>
       <c r="T24">
-        <v>0.8510818771837573</v>
+        <v>0.8593657186981017</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.60736888079406</v>
+        <v>13.97226588597693</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1382681444121166</v>
+        <v>0.1378564318092849</v>
       </c>
       <c r="C25">
-        <v>83.21128386203017</v>
+        <v>82.83718272631687</v>
       </c>
       <c r="D25">
-        <v>100.3701956145952</v>
+        <v>100.8190906420369</v>
       </c>
       <c r="E25">
-        <v>-49.27070456293521</v>
+        <v>-48.4477083997802</v>
       </c>
       <c r="F25">
-        <v>18.92891175256506</v>
+        <v>19.75190791572006</v>
       </c>
       <c r="G25">
         <v>1.77</v>
@@ -3319,28 +3319,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M25">
-        <v>0.9521242611540225</v>
+        <v>0.9935209681607192</v>
       </c>
       <c r="N25">
-        <v>12.35120907217931</v>
+        <v>12.30981236517261</v>
       </c>
       <c r="O25">
-        <v>3.705362721653794</v>
+        <v>3.692943709551784</v>
       </c>
       <c r="P25">
-        <v>8.645846350525519</v>
+        <v>8.616868655620831</v>
       </c>
       <c r="Q25">
-        <v>8.775846350525519</v>
+        <v>8.746868655620831</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1690517459897618</v>
+        <v>0.1702710944859011</v>
       </c>
       <c r="T25">
-        <v>0.8593657186981017</v>
+        <v>0.8678675560417712</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.97226588597693</v>
+        <v>13.39008814072789</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1378564318092849</v>
+        <v>0.1377072192064531</v>
       </c>
       <c r="C26">
-        <v>82.83718272631688</v>
+        <v>82.17786770877498</v>
       </c>
       <c r="D26">
-        <v>100.8190906420369</v>
+        <v>100.9827717876501</v>
       </c>
       <c r="E26">
-        <v>-48.4477083997802</v>
+        <v>-47.6247122366252</v>
       </c>
       <c r="F26">
-        <v>19.75190791572006</v>
+        <v>20.57490407887506</v>
       </c>
       <c r="G26">
         <v>1.77</v>
@@ -3401,45 +3401,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M26">
-        <v>0.993520968160719</v>
+        <v>1.065780031285728</v>
       </c>
       <c r="N26">
-        <v>12.30981236517261</v>
+        <v>12.23755330204761</v>
       </c>
       <c r="O26">
-        <v>3.692943709551784</v>
+        <v>3.671265990614282</v>
       </c>
       <c r="P26">
-        <v>8.616868655620831</v>
+        <v>8.566287311433324</v>
       </c>
       <c r="Q26">
-        <v>8.746868655620831</v>
+        <v>8.696287311433325</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1702710944859011</v>
+        <v>0.1715229589419375</v>
       </c>
       <c r="T26">
-        <v>0.8678675560417712</v>
+        <v>0.8765961090479385</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.39008814072789</v>
+        <v>12.48225050462294</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1377072192064531</v>
+        <v>0.1373060066036214</v>
       </c>
       <c r="C27">
-        <v>82.17786770877498</v>
+        <v>81.79763549318889</v>
       </c>
       <c r="D27">
-        <v>100.9827717876501</v>
+        <v>101.425535735219</v>
       </c>
       <c r="E27">
-        <v>-47.6247122366252</v>
+        <v>-46.8017160734702</v>
       </c>
       <c r="F27">
-        <v>20.57490407887506</v>
+        <v>21.39790024203007</v>
       </c>
       <c r="G27">
         <v>1.77</v>
@@ -3483,28 +3483,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M27">
-        <v>1.065780031285728</v>
+        <v>1.108411232537158</v>
       </c>
       <c r="N27">
-        <v>12.23755330204761</v>
+        <v>12.19492210079618</v>
       </c>
       <c r="O27">
-        <v>3.671265990614282</v>
+        <v>3.658476630238853</v>
       </c>
       <c r="P27">
-        <v>8.566287311433324</v>
+        <v>8.536445470557323</v>
       </c>
       <c r="Q27">
-        <v>8.696287311433325</v>
+        <v>8.666445470557324</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1715229589419375</v>
+        <v>0.1728086575724613</v>
       </c>
       <c r="T27">
-        <v>0.8765961090479385</v>
+        <v>0.8855605688921101</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.48225050462294</v>
+        <v>12.00216394675282</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1373060066036214</v>
+        <v>0.1369047940007896</v>
       </c>
       <c r="C28">
-        <v>81.79763549318889</v>
+        <v>81.42130301696982</v>
       </c>
       <c r="D28">
-        <v>101.425535735219</v>
+        <v>101.8721994221549</v>
       </c>
       <c r="E28">
-        <v>-46.8017160734702</v>
+        <v>-45.97871991031519</v>
       </c>
       <c r="F28">
-        <v>21.39790024203007</v>
+        <v>22.22089640518507</v>
       </c>
       <c r="G28">
         <v>1.77</v>
@@ -3565,28 +3565,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M28">
-        <v>1.108411232537158</v>
+        <v>1.151042433788587</v>
       </c>
       <c r="N28">
-        <v>12.19492210079618</v>
+        <v>12.15229089954475</v>
       </c>
       <c r="O28">
-        <v>3.658476630238853</v>
+        <v>3.645687269863425</v>
       </c>
       <c r="P28">
-        <v>8.536445470557323</v>
+        <v>8.506603629681324</v>
       </c>
       <c r="Q28">
-        <v>8.666445470557324</v>
+        <v>8.636603629681325</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1728086575724613</v>
+        <v>0.1741295808229995</v>
       </c>
       <c r="T28">
-        <v>0.8855605688921101</v>
+        <v>0.8947706303758484</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.00216394675282</v>
+        <v>11.55763935613235</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1369047940007896</v>
+        <v>0.1365035813979579</v>
       </c>
       <c r="C29">
-        <v>81.42130301696982</v>
+        <v>81.04892202971436</v>
       </c>
       <c r="D29">
-        <v>101.8721994221549</v>
+        <v>102.3228145980544</v>
       </c>
       <c r="E29">
-        <v>-45.97871991031519</v>
+        <v>-45.1557237471602</v>
       </c>
       <c r="F29">
-        <v>22.22089640518507</v>
+        <v>23.04389256834007</v>
       </c>
       <c r="G29">
         <v>1.77</v>
@@ -3647,28 +3647,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M29">
-        <v>1.151042433788587</v>
+        <v>1.193673635040016</v>
       </c>
       <c r="N29">
-        <v>12.15229089954475</v>
+        <v>12.10965969829332</v>
       </c>
       <c r="O29">
-        <v>3.645687269863425</v>
+        <v>3.632897909487995</v>
       </c>
       <c r="P29">
-        <v>8.506603629681324</v>
+        <v>8.476761788805323</v>
       </c>
       <c r="Q29">
-        <v>8.636603629681325</v>
+        <v>8.606761788805324</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1741295808229995</v>
+        <v>0.1754871963860526</v>
       </c>
       <c r="T29">
-        <v>0.8947706303758484</v>
+        <v>0.9042365269008013</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.55763935613235</v>
+        <v>11.14486652198477</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1365035813979579</v>
+        <v>0.1361023687951262</v>
       </c>
       <c r="C30">
-        <v>81.04892202971436</v>
+        <v>80.68054520071095</v>
       </c>
       <c r="D30">
-        <v>102.3228145980544</v>
+        <v>102.777433932206</v>
       </c>
       <c r="E30">
-        <v>-45.1557237471602</v>
+        <v>-44.33272758400518</v>
       </c>
       <c r="F30">
-        <v>23.04389256834007</v>
+        <v>23.86688873149508</v>
       </c>
       <c r="G30">
         <v>1.77</v>
@@ -3729,28 +3729,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M30">
-        <v>1.193673635040016</v>
+        <v>1.236304836291445</v>
       </c>
       <c r="N30">
-        <v>12.10965969829332</v>
+        <v>12.06702849704189</v>
       </c>
       <c r="O30">
-        <v>3.632897909487995</v>
+        <v>3.620108549112567</v>
       </c>
       <c r="P30">
-        <v>8.476761788805323</v>
+        <v>8.446919947929322</v>
       </c>
       <c r="Q30">
-        <v>8.606761788805324</v>
+        <v>8.576919947929323</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1754871963860526</v>
+        <v>0.1768830546410228</v>
       </c>
       <c r="T30">
-        <v>0.9042365269008013</v>
+        <v>0.9139690683982883</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.14486652198477</v>
+        <v>10.76056077984736</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1361023687951262</v>
+        <v>0.1357011561922944</v>
       </c>
       <c r="C31">
-        <v>80.68054520071095</v>
+        <v>80.3162261394623</v>
       </c>
       <c r="D31">
-        <v>102.777433932206</v>
+        <v>103.2361110341124</v>
       </c>
       <c r="E31">
-        <v>-44.33272758400519</v>
+        <v>-43.50973142085019</v>
       </c>
       <c r="F31">
-        <v>23.86688873149507</v>
+        <v>24.68988489465008</v>
       </c>
       <c r="G31">
         <v>1.77</v>
@@ -3811,28 +3811,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M31">
-        <v>1.236304836291445</v>
+        <v>1.278936037542874</v>
       </c>
       <c r="N31">
-        <v>12.06702849704189</v>
+        <v>12.02439729579046</v>
       </c>
       <c r="O31">
-        <v>3.620108549112567</v>
+        <v>3.607319188737138</v>
       </c>
       <c r="P31">
-        <v>8.446919947929322</v>
+        <v>8.417078107053323</v>
       </c>
       <c r="Q31">
-        <v>8.576919947929323</v>
+        <v>8.547078107053323</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1768830546410228</v>
+        <v>0.1783187945604206</v>
       </c>
       <c r="T31">
-        <v>0.9139690683982883</v>
+        <v>0.9239796825099892</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.76056077984736</v>
+        <v>10.40187542051912</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1357011561922944</v>
+        <v>0.1352999435894627</v>
       </c>
       <c r="C32">
-        <v>80.3162261394623</v>
+        <v>79.95601941675895</v>
       </c>
       <c r="D32">
-        <v>103.2361110341124</v>
+        <v>103.698900474564</v>
       </c>
       <c r="E32">
-        <v>-43.50973142085019</v>
+        <v>-42.68673525769518</v>
       </c>
       <c r="F32">
-        <v>24.68988489465008</v>
+        <v>25.51288105780508</v>
       </c>
       <c r="G32">
         <v>1.77</v>
@@ -3893,28 +3893,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M32">
-        <v>1.278936037542874</v>
+        <v>1.321567238794303</v>
       </c>
       <c r="N32">
-        <v>12.02439729579046</v>
+        <v>11.98176609453903</v>
       </c>
       <c r="O32">
-        <v>3.607319188737138</v>
+        <v>3.594529828361709</v>
       </c>
       <c r="P32">
-        <v>8.417078107053323</v>
+        <v>8.387236266177322</v>
       </c>
       <c r="Q32">
-        <v>8.547078107053323</v>
+        <v>8.517236266177322</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1783187945604206</v>
+        <v>0.1797961501296561</v>
       </c>
       <c r="T32">
-        <v>0.9239796825099892</v>
+        <v>0.9342804593495653</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.40187542051912</v>
+        <v>10.06633105211527</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1352999435894627</v>
+        <v>0.1352795309866309</v>
       </c>
       <c r="C33">
-        <v>79.95601941675895</v>
+        <v>79.15667966357989</v>
       </c>
       <c r="D33">
-        <v>103.698900474564</v>
+        <v>103.72255688454</v>
       </c>
       <c r="E33">
-        <v>-42.68673525769518</v>
+        <v>-41.86373909454018</v>
       </c>
       <c r="F33">
-        <v>25.51288105780508</v>
+        <v>26.33587722096008</v>
       </c>
       <c r="G33">
         <v>1.77</v>
@@ -3975,45 +3975,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M33">
-        <v>1.321567238794303</v>
+        <v>1.408969431321364</v>
       </c>
       <c r="N33">
-        <v>11.98176609453903</v>
+        <v>11.89436390201197</v>
       </c>
       <c r="O33">
-        <v>3.594529828361709</v>
+        <v>3.568309170603591</v>
       </c>
       <c r="P33">
-        <v>8.387236266177322</v>
+        <v>8.32605473140838</v>
       </c>
       <c r="Q33">
-        <v>8.517236266177322</v>
+        <v>8.456054731408381</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1797961501296561</v>
+        <v>0.1813169573332808</v>
       </c>
       <c r="T33">
-        <v>0.9342804593495653</v>
+        <v>0.944884200213835</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>10.06633105211527</v>
+        <v>9.441889254373077</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1352795309866309</v>
+        <v>0.1348902183837992</v>
       </c>
       <c r="C34">
-        <v>79.15667966357989</v>
+        <v>78.78693750884055</v>
       </c>
       <c r="D34">
-        <v>103.72255688454</v>
+        <v>104.1758108929556</v>
       </c>
       <c r="E34">
-        <v>-41.86373909454018</v>
+        <v>-41.04074293138518</v>
       </c>
       <c r="F34">
-        <v>26.33587722096008</v>
+        <v>27.15887338411509</v>
       </c>
       <c r="G34">
         <v>1.77</v>
@@ -4057,28 +4057,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M34">
-        <v>1.408969431321364</v>
+        <v>1.452999726050157</v>
       </c>
       <c r="N34">
-        <v>11.89436390201197</v>
+        <v>11.85033360728318</v>
       </c>
       <c r="O34">
-        <v>3.568309170603591</v>
+        <v>3.555100082184953</v>
       </c>
       <c r="P34">
-        <v>8.32605473140838</v>
+        <v>8.295233525098224</v>
       </c>
       <c r="Q34">
-        <v>8.456054731408381</v>
+        <v>8.425233525098225</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1813169573332808</v>
+        <v>0.1828831617668645</v>
       </c>
       <c r="T34">
-        <v>0.944884200213835</v>
+        <v>0.9558044706561427</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.441889254373077</v>
+        <v>9.155771398179953</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1348902183837992</v>
+        <v>0.1345009057809674</v>
       </c>
       <c r="C35">
-        <v>78.78693750884055</v>
+        <v>78.42117406201194</v>
       </c>
       <c r="D35">
-        <v>104.1758108929556</v>
+        <v>104.633043609282</v>
       </c>
       <c r="E35">
-        <v>-41.04074293138518</v>
+        <v>-40.21774676823017</v>
       </c>
       <c r="F35">
-        <v>27.15887338411509</v>
+        <v>27.98186954727009</v>
       </c>
       <c r="G35">
         <v>1.77</v>
@@ -4139,28 +4139,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M35">
-        <v>1.452999726050157</v>
+        <v>1.49703002077895</v>
       </c>
       <c r="N35">
-        <v>11.85033360728318</v>
+        <v>11.80630331255438</v>
       </c>
       <c r="O35">
-        <v>3.555100082184953</v>
+        <v>3.541890993766315</v>
       </c>
       <c r="P35">
-        <v>8.295233525098224</v>
+        <v>8.264412318788068</v>
       </c>
       <c r="Q35">
-        <v>8.425233525098225</v>
+        <v>8.394412318788069</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1828831617668645</v>
+        <v>0.1844968269408598</v>
       </c>
       <c r="T35">
-        <v>0.9558044706561427</v>
+        <v>0.9670556583845807</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.155771398179953</v>
+        <v>8.886484004115836</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1345009057809674</v>
+        <v>0.1341115931781357</v>
       </c>
       <c r="C36">
-        <v>78.42117406201194</v>
+        <v>78.05944194227159</v>
       </c>
       <c r="D36">
-        <v>104.633043609282</v>
+        <v>105.0943076526967</v>
       </c>
       <c r="E36">
-        <v>-40.21774676823017</v>
+        <v>-39.39475060507517</v>
       </c>
       <c r="F36">
-        <v>27.98186954727009</v>
+        <v>28.80486571042509</v>
       </c>
       <c r="G36">
         <v>1.77</v>
@@ -4221,28 +4221,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M36">
-        <v>1.49703002077895</v>
+        <v>1.541060315507742</v>
       </c>
       <c r="N36">
-        <v>11.80630331255438</v>
+        <v>11.76227301782559</v>
       </c>
       <c r="O36">
-        <v>3.541890993766315</v>
+        <v>3.528681905347677</v>
       </c>
       <c r="P36">
-        <v>8.264412318788068</v>
+        <v>8.233591112477914</v>
       </c>
       <c r="Q36">
-        <v>8.394412318788069</v>
+        <v>8.363591112477915</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1844968269408598</v>
+        <v>0.186160143350978</v>
       </c>
       <c r="T36">
-        <v>0.9670556583845807</v>
+        <v>0.9786530365046631</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.886484004115836</v>
+        <v>8.632584461141096</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1341115931781357</v>
+        <v>0.133722280575304</v>
       </c>
       <c r="C37">
-        <v>78.05944194227159</v>
+        <v>77.70179470077049</v>
       </c>
       <c r="D37">
-        <v>105.0943076526967</v>
+        <v>105.5596565743506</v>
       </c>
       <c r="E37">
-        <v>-39.39475060507517</v>
+        <v>-38.57175444192016</v>
       </c>
       <c r="F37">
-        <v>28.80486571042509</v>
+        <v>29.6278618735801</v>
       </c>
       <c r="G37">
         <v>1.77</v>
@@ -4303,28 +4303,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M37">
-        <v>1.541060315507742</v>
+        <v>1.585090610236535</v>
       </c>
       <c r="N37">
-        <v>11.76227301782559</v>
+        <v>11.7182427230968</v>
       </c>
       <c r="O37">
-        <v>3.528681905347677</v>
+        <v>3.51547281692904</v>
       </c>
       <c r="P37">
-        <v>8.233591112477914</v>
+        <v>8.202769906167759</v>
       </c>
       <c r="Q37">
-        <v>8.363591112477915</v>
+        <v>8.33276990616776</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.186160143350978</v>
+        <v>0.1878754383989125</v>
       </c>
       <c r="T37">
-        <v>0.9786530365046631</v>
+        <v>0.990612832690998</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.632584461141096</v>
+        <v>8.392790448331622</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.133722280575304</v>
+        <v>0.1333329679724722</v>
       </c>
       <c r="C38">
-        <v>77.70179470077051</v>
+        <v>77.34828684135847</v>
       </c>
       <c r="D38">
-        <v>105.5596565743506</v>
+        <v>106.0291448780936</v>
       </c>
       <c r="E38">
-        <v>-38.57175444192018</v>
+        <v>-37.74875827876517</v>
       </c>
       <c r="F38">
-        <v>29.62786187358009</v>
+        <v>30.4508580367351</v>
       </c>
       <c r="G38">
         <v>1.77</v>
@@ -4385,28 +4385,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M38">
-        <v>1.585090610236535</v>
+        <v>1.629120904965327</v>
       </c>
       <c r="N38">
-        <v>11.7182427230968</v>
+        <v>11.67421242836801</v>
       </c>
       <c r="O38">
-        <v>3.51547281692904</v>
+        <v>3.502263728510402</v>
       </c>
       <c r="P38">
-        <v>8.202769906167759</v>
+        <v>8.171948699857605</v>
       </c>
       <c r="Q38">
-        <v>8.33276990616776</v>
+        <v>8.301948699857606</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1878754383989125</v>
+        <v>0.1896451872578924</v>
       </c>
       <c r="T38">
-        <v>0.990612832690998</v>
+        <v>1.00295230494674</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.392790448331624</v>
+        <v>8.165958274052389</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1333329679724722</v>
+        <v>0.1329436553696405</v>
       </c>
       <c r="C39">
-        <v>77.34828684135847</v>
+        <v>76.99897384186491</v>
       </c>
       <c r="D39">
-        <v>106.0291448780936</v>
+        <v>106.502828041755</v>
       </c>
       <c r="E39">
-        <v>-37.74875827876517</v>
+        <v>-36.92576211561017</v>
       </c>
       <c r="F39">
-        <v>30.4508580367351</v>
+        <v>31.2738541998901</v>
       </c>
       <c r="G39">
         <v>1.77</v>
@@ -4467,28 +4467,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M39">
-        <v>1.629120904965327</v>
+        <v>1.67315119969412</v>
       </c>
       <c r="N39">
-        <v>11.67421242836801</v>
+        <v>11.63018213363921</v>
       </c>
       <c r="O39">
-        <v>3.502263728510402</v>
+        <v>3.489054640091764</v>
       </c>
       <c r="P39">
-        <v>8.171948699857605</v>
+        <v>8.141127493547451</v>
       </c>
       <c r="Q39">
-        <v>8.301948699857606</v>
+        <v>8.271127493547452</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1896451872578924</v>
+        <v>0.1914720247897427</v>
       </c>
       <c r="T39">
-        <v>1.00295230494674</v>
+        <v>1.015689824694603</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.165958274052389</v>
+        <v>7.951064635261538</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1329436553696405</v>
+        <v>0.1325543427668087</v>
       </c>
       <c r="C40">
-        <v>76.99897384186491</v>
+        <v>76.65391217595266</v>
       </c>
       <c r="D40">
-        <v>106.502828041755</v>
+        <v>106.9807625389978</v>
       </c>
       <c r="E40">
-        <v>-36.92576211561017</v>
+        <v>-36.10276595245517</v>
       </c>
       <c r="F40">
-        <v>31.2738541998901</v>
+        <v>32.0968503630451</v>
       </c>
       <c r="G40">
         <v>1.77</v>
@@ -4549,28 +4549,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M40">
-        <v>1.67315119969412</v>
+        <v>1.717181494422913</v>
       </c>
       <c r="N40">
-        <v>11.63018213363921</v>
+        <v>11.58615183891042</v>
       </c>
       <c r="O40">
-        <v>3.489054640091764</v>
+        <v>3.475845551673126</v>
       </c>
       <c r="P40">
-        <v>8.141127493547451</v>
+        <v>8.110306287237295</v>
       </c>
       <c r="Q40">
-        <v>8.271127493547452</v>
+        <v>8.240306287237296</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1914720247897427</v>
+        <v>0.1933587586341127</v>
       </c>
       <c r="T40">
-        <v>1.015689824694603</v>
+        <v>1.028844968040757</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.951064635261538</v>
+        <v>7.747191183075344</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1325543427668087</v>
+        <v>0.132389030163977</v>
       </c>
       <c r="C41">
-        <v>76.65391217595266</v>
+        <v>76.03515976370643</v>
       </c>
       <c r="D41">
-        <v>106.9807625389978</v>
+        <v>107.1850062899065</v>
       </c>
       <c r="E41">
-        <v>-36.10276595245517</v>
+        <v>-35.27976978930016</v>
       </c>
       <c r="F41">
-        <v>32.0968503630451</v>
+        <v>32.9198465262001</v>
       </c>
       <c r="G41">
         <v>1.77</v>
@@ -4631,45 +4631,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M41">
-        <v>1.717181494422913</v>
+        <v>1.787547666372666</v>
       </c>
       <c r="N41">
-        <v>11.58615183891042</v>
+        <v>11.51578566696067</v>
       </c>
       <c r="O41">
-        <v>3.475845551673126</v>
+        <v>3.454735700088201</v>
       </c>
       <c r="P41">
-        <v>8.110306287237295</v>
+        <v>8.061049966872469</v>
       </c>
       <c r="Q41">
-        <v>8.240306287237296</v>
+        <v>8.19104996687247</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1933587586341127</v>
+        <v>0.1953083836066284</v>
       </c>
       <c r="T41">
-        <v>1.028844968040757</v>
+        <v>1.042438616165116</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.747191183075344</v>
+        <v>7.442225784294063</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.132389030163977</v>
+        <v>0.1320053175611453</v>
       </c>
       <c r="C42">
-        <v>76.03515976370643</v>
+        <v>75.68925989706315</v>
       </c>
       <c r="D42">
-        <v>107.1850062899065</v>
+        <v>107.6621025864183</v>
       </c>
       <c r="E42">
-        <v>-35.27976978930016</v>
+        <v>-34.45677362614516</v>
       </c>
       <c r="F42">
-        <v>32.9198465262001</v>
+        <v>33.74284268935511</v>
       </c>
       <c r="G42">
         <v>1.77</v>
@@ -4713,28 +4713,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M42">
-        <v>1.787547666372666</v>
+        <v>1.832236358031982</v>
       </c>
       <c r="N42">
-        <v>11.51578566696067</v>
+        <v>11.47109697530135</v>
       </c>
       <c r="O42">
-        <v>3.454735700088201</v>
+        <v>3.441329092590406</v>
       </c>
       <c r="P42">
-        <v>8.061049966872469</v>
+        <v>8.029767882710946</v>
       </c>
       <c r="Q42">
-        <v>8.19104996687247</v>
+        <v>8.159767882710947</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1953083836066284</v>
+        <v>0.1973240975612632</v>
       </c>
       <c r="T42">
-        <v>1.042438616165116</v>
+        <v>1.056493065920809</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.442225784294063</v>
+        <v>7.26070808223811</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1320053175611453</v>
+        <v>0.1316216049583135</v>
       </c>
       <c r="C43">
-        <v>75.68925989706315</v>
+        <v>75.3476262722787</v>
       </c>
       <c r="D43">
-        <v>107.6621025864183</v>
+        <v>108.1434651247888</v>
       </c>
       <c r="E43">
-        <v>-34.45677362614516</v>
+        <v>-33.63377746299015</v>
       </c>
       <c r="F43">
-        <v>33.74284268935511</v>
+        <v>34.56583885251011</v>
       </c>
       <c r="G43">
         <v>1.77</v>
@@ -4795,28 +4795,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M43">
-        <v>1.832236358031982</v>
+        <v>1.876925049691299</v>
       </c>
       <c r="N43">
-        <v>11.47109697530135</v>
+        <v>11.42640828364204</v>
       </c>
       <c r="O43">
-        <v>3.441329092590406</v>
+        <v>3.427922485092611</v>
       </c>
       <c r="P43">
-        <v>8.029767882710946</v>
+        <v>7.998485798549426</v>
       </c>
       <c r="Q43">
-        <v>8.159767882710947</v>
+        <v>8.128485798549427</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1973240975612632</v>
+        <v>0.199409318893644</v>
       </c>
       <c r="T43">
-        <v>1.056493065920809</v>
+        <v>1.071032151874974</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.26070808223811</v>
+        <v>7.087834080280061</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1316216049583135</v>
+        <v>0.1312378923554818</v>
       </c>
       <c r="C44">
-        <v>75.34762627227872</v>
+        <v>75.01031637008182</v>
       </c>
       <c r="D44">
-        <v>108.1434651247888</v>
+        <v>108.6291513857469</v>
       </c>
       <c r="E44">
-        <v>-33.63377746299016</v>
+        <v>-32.81078129983516</v>
       </c>
       <c r="F44">
-        <v>34.5658388525101</v>
+        <v>35.38883501566511</v>
       </c>
       <c r="G44">
         <v>1.77</v>
@@ -4877,28 +4877,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M44">
-        <v>1.876925049691299</v>
+        <v>1.921613741350615</v>
       </c>
       <c r="N44">
-        <v>11.42640828364204</v>
+        <v>11.38171959198272</v>
       </c>
       <c r="O44">
-        <v>3.427922485092611</v>
+        <v>3.414515877594816</v>
       </c>
       <c r="P44">
-        <v>7.998485798549426</v>
+        <v>7.967203714387903</v>
       </c>
       <c r="Q44">
-        <v>8.128485798549427</v>
+        <v>8.097203714387904</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.199409318893644</v>
+        <v>0.2015677058868102</v>
       </c>
       <c r="T44">
-        <v>1.071032151874974</v>
+        <v>1.086081381195952</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.087834080280062</v>
+        <v>6.923000729575874</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1312378923554818</v>
+        <v>0.13085417975265</v>
       </c>
       <c r="C45">
-        <v>75.01031637008182</v>
+        <v>74.6773887084731</v>
       </c>
       <c r="D45">
-        <v>108.6291513857469</v>
+        <v>109.1192198872932</v>
       </c>
       <c r="E45">
-        <v>-32.81078129983516</v>
+        <v>-31.98778513668015</v>
       </c>
       <c r="F45">
-        <v>35.38883501566511</v>
+        <v>36.21183117882011</v>
       </c>
       <c r="G45">
         <v>1.77</v>
@@ -4959,28 +4959,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M45">
-        <v>1.921613741350615</v>
+        <v>1.966302433009932</v>
       </c>
       <c r="N45">
-        <v>11.38171959198272</v>
+        <v>11.3370309003234</v>
       </c>
       <c r="O45">
-        <v>3.414515877594816</v>
+        <v>3.401109270097021</v>
       </c>
       <c r="P45">
-        <v>7.967203714387903</v>
+        <v>7.935921630226382</v>
       </c>
       <c r="Q45">
-        <v>8.097203714387904</v>
+        <v>8.065921630226383</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2015677058868102</v>
+        <v>0.2038031781297322</v>
       </c>
       <c r="T45">
-        <v>1.086081381195952</v>
+        <v>1.101668082992679</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.923000729575874</v>
+        <v>6.765659803903694</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.13085417975265</v>
+        <v>0.1304704671498183</v>
       </c>
       <c r="C46">
-        <v>74.6773887084731</v>
+        <v>74.34890286622887</v>
       </c>
       <c r="D46">
-        <v>109.1192198872932</v>
+        <v>109.613730208204</v>
       </c>
       <c r="E46">
-        <v>-31.98778513668015</v>
+        <v>-31.16478897352515</v>
       </c>
       <c r="F46">
-        <v>36.21183117882011</v>
+        <v>37.03482734197512</v>
       </c>
       <c r="G46">
         <v>1.77</v>
@@ -5041,28 +5041,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M46">
-        <v>1.966302433009932</v>
+        <v>2.010991124669249</v>
       </c>
       <c r="N46">
-        <v>11.3370309003234</v>
+        <v>11.29234220866408</v>
       </c>
       <c r="O46">
-        <v>3.401109270097021</v>
+        <v>3.387702662599225</v>
       </c>
       <c r="P46">
-        <v>7.935921630226382</v>
+        <v>7.90463954606486</v>
       </c>
       <c r="Q46">
-        <v>8.065921630226383</v>
+        <v>8.034639546064859</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2038031781297322</v>
+        <v>0.2061199402723969</v>
       </c>
       <c r="T46">
-        <v>1.101668082992679</v>
+        <v>1.117821573945651</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.765659803903694</v>
+        <v>6.61531180826139</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1304704671498183</v>
+        <v>0.1300867545469866</v>
       </c>
       <c r="C47">
-        <v>74.34890286622887</v>
+        <v>74.024919507047</v>
       </c>
       <c r="D47">
-        <v>109.613730208204</v>
+        <v>110.1127430121771</v>
       </c>
       <c r="E47">
-        <v>-31.16478897352515</v>
+        <v>-30.34179281037014</v>
       </c>
       <c r="F47">
-        <v>37.03482734197512</v>
+        <v>37.85782350513012</v>
       </c>
       <c r="G47">
         <v>1.77</v>
@@ -5123,28 +5123,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M47">
-        <v>2.010991124669249</v>
+        <v>2.055679816328566</v>
       </c>
       <c r="N47">
-        <v>11.29234220866408</v>
+        <v>11.24765351700477</v>
       </c>
       <c r="O47">
-        <v>3.387702662599225</v>
+        <v>3.374296055101431</v>
       </c>
       <c r="P47">
-        <v>7.90463954606486</v>
+        <v>7.873357461903339</v>
       </c>
       <c r="Q47">
-        <v>8.034639546064859</v>
+        <v>8.00335746190334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2061199402723969</v>
+        <v>0.2085225084203455</v>
       </c>
       <c r="T47">
-        <v>1.117821573945651</v>
+        <v>1.134573342341326</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.61531180826139</v>
+        <v>6.471500681994837</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1300867545469866</v>
+        <v>0.1297030419441548</v>
       </c>
       <c r="C48">
-        <v>74.024919507047</v>
+        <v>73.70550040435504</v>
       </c>
       <c r="D48">
-        <v>110.1127430121771</v>
+        <v>110.6163200726402</v>
       </c>
       <c r="E48">
-        <v>-30.34179281037014</v>
+        <v>-29.51879664721514</v>
       </c>
       <c r="F48">
-        <v>37.85782350513012</v>
+        <v>38.68081966828512</v>
       </c>
       <c r="G48">
         <v>1.77</v>
@@ -5205,28 +5205,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M48">
-        <v>2.055679816328566</v>
+        <v>2.100368507987882</v>
       </c>
       <c r="N48">
-        <v>11.24765351700477</v>
+        <v>11.20296482534545</v>
       </c>
       <c r="O48">
-        <v>3.374296055101431</v>
+        <v>3.360889447603636</v>
       </c>
       <c r="P48">
-        <v>7.873357461903339</v>
+        <v>7.842075377741816</v>
       </c>
       <c r="Q48">
-        <v>8.00335746190334</v>
+        <v>7.972075377741816</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2085225084203455</v>
+        <v>0.2110157395172733</v>
       </c>
       <c r="T48">
-        <v>1.134573342341326</v>
+        <v>1.151957252940611</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.471500681994837</v>
+        <v>6.333809178122606</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1297030419441548</v>
+        <v>0.1293193293413231</v>
       </c>
       <c r="C49">
-        <v>73.70550040435504</v>
+        <v>73.39070846680247</v>
       </c>
       <c r="D49">
-        <v>110.6163200726402</v>
+        <v>111.1245242982426</v>
       </c>
       <c r="E49">
-        <v>-29.51879664721514</v>
+        <v>-28.69580048406014</v>
       </c>
       <c r="F49">
-        <v>38.68081966828512</v>
+        <v>39.50381583144013</v>
       </c>
       <c r="G49">
         <v>1.77</v>
@@ -5287,28 +5287,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M49">
-        <v>2.100368507987882</v>
+        <v>2.145057199647199</v>
       </c>
       <c r="N49">
-        <v>11.20296482534545</v>
+        <v>11.15827613368613</v>
       </c>
       <c r="O49">
-        <v>3.360889447603636</v>
+        <v>3.34748284010584</v>
       </c>
       <c r="P49">
-        <v>7.842075377741816</v>
+        <v>7.810793293580295</v>
       </c>
       <c r="Q49">
-        <v>7.972075377741816</v>
+        <v>7.940793293580295</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2110157395172733</v>
+        <v>0.213604864117929</v>
       </c>
       <c r="T49">
-        <v>1.151957252940611</v>
+        <v>1.170009775486022</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.333809178122606</v>
+        <v>6.201854820245051</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1293193293413231</v>
+        <v>0.1292786167384914</v>
       </c>
       <c r="C50">
-        <v>73.39070846680247</v>
+        <v>72.62190784256961</v>
       </c>
       <c r="D50">
-        <v>111.1245242982426</v>
+        <v>111.1787198371647</v>
       </c>
       <c r="E50">
-        <v>-28.69580048406014</v>
+        <v>-27.87280432090514</v>
       </c>
       <c r="F50">
-        <v>39.50381583144012</v>
+        <v>40.32681199459513</v>
       </c>
       <c r="G50">
         <v>1.77</v>
@@ -5369,45 +5369,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M50">
-        <v>2.145057199647199</v>
+        <v>2.230072703301111</v>
       </c>
       <c r="N50">
-        <v>11.15827613368614</v>
+        <v>11.07326063003222</v>
       </c>
       <c r="O50">
-        <v>3.347482840105841</v>
+        <v>3.321978189009667</v>
       </c>
       <c r="P50">
-        <v>7.810793293580296</v>
+        <v>7.751282441022557</v>
       </c>
       <c r="Q50">
-        <v>7.940793293580296</v>
+        <v>7.881282441022557</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.213604864117929</v>
+        <v>0.2162955230166497</v>
       </c>
       <c r="T50">
-        <v>1.170009775486022</v>
+        <v>1.188770240092037</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.201854820245053</v>
+        <v>5.965425841785698</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1292786167384914</v>
+        <v>0.1289019041356596</v>
       </c>
       <c r="C51">
-        <v>72.62190784256961</v>
+        <v>72.30290043111624</v>
       </c>
       <c r="D51">
-        <v>111.1787198371647</v>
+        <v>111.6827085888664</v>
       </c>
       <c r="E51">
-        <v>-27.87280432090514</v>
+        <v>-27.04980815775014</v>
       </c>
       <c r="F51">
-        <v>40.32681199459513</v>
+        <v>41.14980815775013</v>
       </c>
       <c r="G51">
         <v>1.77</v>
@@ -5451,28 +5451,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M51">
-        <v>2.230072703301111</v>
+        <v>2.275584391123582</v>
       </c>
       <c r="N51">
-        <v>11.07326063003222</v>
+        <v>11.02774894220975</v>
       </c>
       <c r="O51">
-        <v>3.321978189009667</v>
+        <v>3.308324682662926</v>
       </c>
       <c r="P51">
-        <v>7.751282441022557</v>
+        <v>7.719424259546827</v>
       </c>
       <c r="Q51">
-        <v>7.881282441022557</v>
+        <v>7.849424259546827</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2162955230166497</v>
+        <v>0.2190938082713192</v>
       </c>
       <c r="T51">
-        <v>1.188770240092037</v>
+        <v>1.208281123282293</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.965425841785698</v>
+        <v>5.846117324949984</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1289019041356596</v>
+        <v>0.1285251915328279</v>
       </c>
       <c r="C52">
-        <v>72.30290043111624</v>
+        <v>71.98848313087163</v>
       </c>
       <c r="D52">
-        <v>111.6827085888664</v>
+        <v>112.1912874517768</v>
       </c>
       <c r="E52">
-        <v>-27.04980815775014</v>
+        <v>-26.22681199459513</v>
       </c>
       <c r="F52">
-        <v>41.14980815775013</v>
+        <v>41.97280432090513</v>
       </c>
       <c r="G52">
         <v>1.77</v>
@@ -5533,28 +5533,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M52">
-        <v>2.275584391123582</v>
+        <v>2.321096078946054</v>
       </c>
       <c r="N52">
-        <v>11.02774894220975</v>
+        <v>10.98223725438728</v>
       </c>
       <c r="O52">
-        <v>3.308324682662926</v>
+        <v>3.294671176316184</v>
       </c>
       <c r="P52">
-        <v>7.719424259546827</v>
+        <v>7.687566078071097</v>
       </c>
       <c r="Q52">
-        <v>7.849424259546827</v>
+        <v>7.817566078071096</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2190938082713192</v>
+        <v>0.2220063092506692</v>
       </c>
       <c r="T52">
-        <v>1.208281123282293</v>
+        <v>1.228588369051744</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.846117324949984</v>
+        <v>5.731487573480377</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1285251915328279</v>
+        <v>0.1281484789299961</v>
       </c>
       <c r="C53">
-        <v>71.98848313087163</v>
+        <v>71.67871893581324</v>
       </c>
       <c r="D53">
-        <v>112.1912874517768</v>
+        <v>112.7045194198734</v>
       </c>
       <c r="E53">
-        <v>-26.22681199459513</v>
+        <v>-25.40381583144013</v>
       </c>
       <c r="F53">
-        <v>41.97280432090513</v>
+        <v>42.79580048406014</v>
       </c>
       <c r="G53">
         <v>1.77</v>
@@ -5615,28 +5615,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M53">
-        <v>2.321096078946054</v>
+        <v>2.366607766768526</v>
       </c>
       <c r="N53">
-        <v>10.98223725438728</v>
+        <v>10.93672556656481</v>
       </c>
       <c r="O53">
-        <v>3.294671176316184</v>
+        <v>3.281017669969442</v>
       </c>
       <c r="P53">
-        <v>7.687566078071097</v>
+        <v>7.655707896595366</v>
       </c>
       <c r="Q53">
-        <v>7.817566078071096</v>
+        <v>7.785707896595366</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2220063092506692</v>
+        <v>0.225040164437492</v>
       </c>
       <c r="T53">
-        <v>1.228588369051744</v>
+        <v>1.249741750061588</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.731487573480377</v>
+        <v>5.621266658605753</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1281484789299961</v>
+        <v>0.1277717663271644</v>
       </c>
       <c r="C54">
-        <v>71.67871893581324</v>
+        <v>71.37367199790859</v>
       </c>
       <c r="D54">
-        <v>112.7045194198734</v>
+        <v>113.2224686451237</v>
       </c>
       <c r="E54">
-        <v>-25.40381583144013</v>
+        <v>-24.58081966828512</v>
       </c>
       <c r="F54">
-        <v>42.79580048406014</v>
+        <v>43.61879664721514</v>
       </c>
       <c r="G54">
         <v>1.77</v>
@@ -5697,28 +5697,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M54">
-        <v>2.366607766768526</v>
+        <v>2.412119454590997</v>
       </c>
       <c r="N54">
-        <v>10.93672556656481</v>
+        <v>10.89121387874234</v>
       </c>
       <c r="O54">
-        <v>3.281017669969442</v>
+        <v>3.267364163622701</v>
       </c>
       <c r="P54">
-        <v>7.655707896595366</v>
+        <v>7.623849715119636</v>
       </c>
       <c r="Q54">
-        <v>7.785707896595366</v>
+        <v>7.753849715119636</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.225040164437492</v>
+        <v>0.2282031198450306</v>
       </c>
       <c r="T54">
-        <v>1.249741750061588</v>
+        <v>1.271795274944191</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.621266658605753</v>
+        <v>5.51520502353772</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1277717663271644</v>
+        <v>0.1273950537243327</v>
       </c>
       <c r="C55">
-        <v>71.37367199790859</v>
+        <v>71.07340765384697</v>
       </c>
       <c r="D55">
-        <v>113.2224686451237</v>
+        <v>113.7452004642171</v>
       </c>
       <c r="E55">
-        <v>-24.58081966828512</v>
+        <v>-23.75782350513012</v>
       </c>
       <c r="F55">
-        <v>43.61879664721514</v>
+        <v>44.44179281037015</v>
       </c>
       <c r="G55">
         <v>1.77</v>
@@ -5779,28 +5779,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M55">
-        <v>2.412119454590997</v>
+        <v>2.457631142413469</v>
       </c>
       <c r="N55">
-        <v>10.89121387874234</v>
+        <v>10.84570219091987</v>
       </c>
       <c r="O55">
-        <v>3.267364163622701</v>
+        <v>3.25371065727596</v>
       </c>
       <c r="P55">
-        <v>7.623849715119636</v>
+        <v>7.591991533643906</v>
       </c>
       <c r="Q55">
-        <v>7.753849715119636</v>
+        <v>7.721991533643906</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2282031198450306</v>
+        <v>0.2315035950528971</v>
       </c>
       <c r="T55">
-        <v>1.271795274944191</v>
+        <v>1.294807648734734</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.51520502353772</v>
+        <v>5.413071597175911</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1273950537243327</v>
+        <v>0.1270183411215009</v>
       </c>
       <c r="C56">
-        <v>71.07340765384697</v>
+        <v>70.77799245251424</v>
       </c>
       <c r="D56">
-        <v>113.7452004642171</v>
+        <v>114.2727814260394</v>
       </c>
       <c r="E56">
-        <v>-23.75782350513012</v>
+        <v>-22.93482734197512</v>
       </c>
       <c r="F56">
-        <v>44.44179281037015</v>
+        <v>45.26478897352515</v>
       </c>
       <c r="G56">
         <v>1.77</v>
@@ -5861,28 +5861,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M56">
-        <v>2.457631142413469</v>
+        <v>2.503142830235941</v>
       </c>
       <c r="N56">
-        <v>10.84570219091987</v>
+        <v>10.80019050309739</v>
       </c>
       <c r="O56">
-        <v>3.25371065727596</v>
+        <v>3.240057150929218</v>
       </c>
       <c r="P56">
-        <v>7.591991533643906</v>
+        <v>7.560133352168176</v>
       </c>
       <c r="Q56">
-        <v>7.721991533643906</v>
+        <v>7.690133352168176</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2315035950528971</v>
+        <v>0.2349507580477798</v>
       </c>
       <c r="T56">
-        <v>1.294807648734734</v>
+        <v>1.318842794693745</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.413071597175911</v>
+        <v>5.314652113590894</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1270183411215009</v>
+        <v>0.1266416285186692</v>
       </c>
       <c r="C57">
-        <v>70.77799245251424</v>
+        <v>70.48749418323686</v>
       </c>
       <c r="D57">
-        <v>114.2727814260394</v>
+        <v>114.805279319917</v>
       </c>
       <c r="E57">
-        <v>-22.93482734197512</v>
+        <v>-22.11183117882012</v>
       </c>
       <c r="F57">
-        <v>45.26478897352515</v>
+        <v>46.08778513668015</v>
       </c>
       <c r="G57">
         <v>1.77</v>
@@ -5943,28 +5943,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M57">
-        <v>2.503142830235941</v>
+        <v>2.548654518058412</v>
       </c>
       <c r="N57">
-        <v>10.80019050309739</v>
+        <v>10.75467881527492</v>
       </c>
       <c r="O57">
-        <v>3.240057150929218</v>
+        <v>3.226403644582476</v>
       </c>
       <c r="P57">
-        <v>7.560133352168176</v>
+        <v>7.528275170692446</v>
       </c>
       <c r="Q57">
-        <v>7.690133352168176</v>
+        <v>7.658275170692446</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2349507580477798</v>
+        <v>0.2385546102697027</v>
       </c>
       <c r="T57">
-        <v>1.318842794693745</v>
+        <v>1.343970447287257</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.314652113590894</v>
+        <v>5.219747611562485</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1266416285186692</v>
+        <v>0.1262649159158374</v>
       </c>
       <c r="C58">
-        <v>70.48749418323686</v>
+        <v>70.20198190481824</v>
       </c>
       <c r="D58">
-        <v>114.805279319917</v>
+        <v>115.3427632046534</v>
       </c>
       <c r="E58">
-        <v>-22.11183117882012</v>
+        <v>-21.28883501566511</v>
       </c>
       <c r="F58">
-        <v>46.08778513668015</v>
+        <v>46.91078129983515</v>
       </c>
       <c r="G58">
         <v>1.77</v>
@@ -6025,28 +6025,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M58">
-        <v>2.548654518058412</v>
+        <v>2.594166205880884</v>
       </c>
       <c r="N58">
-        <v>10.75467881527492</v>
+        <v>10.70916712745245</v>
       </c>
       <c r="O58">
-        <v>3.226403644582476</v>
+        <v>3.212750138235735</v>
       </c>
       <c r="P58">
-        <v>7.528275170692446</v>
+        <v>7.496416989216716</v>
       </c>
       <c r="Q58">
-        <v>7.658275170692446</v>
+        <v>7.626416989216716</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2385546102697027</v>
+        <v>0.2423260835252034</v>
       </c>
       <c r="T58">
-        <v>1.343970447287257</v>
+        <v>1.370266827908374</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.219747611562485</v>
+        <v>5.128173092061389</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1262649159158374</v>
+        <v>0.1258882033130057</v>
       </c>
       <c r="C59">
-        <v>70.20198190481824</v>
+        <v>69.92152597539547</v>
       </c>
       <c r="D59">
-        <v>115.3427632046534</v>
+        <v>115.8853034383856</v>
       </c>
       <c r="E59">
-        <v>-21.28883501566511</v>
+        <v>-20.46583885251011</v>
       </c>
       <c r="F59">
-        <v>46.91078129983515</v>
+        <v>47.73377746299015</v>
       </c>
       <c r="G59">
         <v>1.77</v>
@@ -6107,28 +6107,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M59">
-        <v>2.594166205880884</v>
+        <v>2.639677893703356</v>
       </c>
       <c r="N59">
-        <v>10.70916712745245</v>
+        <v>10.66365543962998</v>
       </c>
       <c r="O59">
-        <v>3.212750138235735</v>
+        <v>3.199096631888994</v>
       </c>
       <c r="P59">
-        <v>7.496416989216716</v>
+        <v>7.464558807740985</v>
       </c>
       <c r="Q59">
-        <v>7.626416989216716</v>
+        <v>7.594558807740985</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2423260835252034</v>
+        <v>0.2462771507452517</v>
       </c>
       <c r="T59">
-        <v>1.370266827908374</v>
+        <v>1.397815417130496</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.128173092061389</v>
+        <v>5.039756314612054</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1258882033130057</v>
+        <v>0.125511490710174</v>
       </c>
       <c r="C60">
-        <v>69.92152597539544</v>
+        <v>69.64619808314194</v>
       </c>
       <c r="D60">
-        <v>115.8853034383856</v>
+        <v>116.4329717092871</v>
       </c>
       <c r="E60">
-        <v>-20.46583885251012</v>
+        <v>-19.64284268935511</v>
       </c>
       <c r="F60">
-        <v>47.73377746299015</v>
+        <v>48.55677362614515</v>
       </c>
       <c r="G60">
         <v>1.77</v>
@@ -6189,28 +6189,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M60">
-        <v>2.639677893703355</v>
+        <v>2.685189581525827</v>
       </c>
       <c r="N60">
-        <v>10.66365543962998</v>
+        <v>10.61814375180751</v>
       </c>
       <c r="O60">
-        <v>3.199096631888994</v>
+        <v>3.185443125542252</v>
       </c>
       <c r="P60">
-        <v>7.464558807740985</v>
+        <v>7.432700626265256</v>
       </c>
       <c r="Q60">
-        <v>7.594558807740985</v>
+        <v>7.562700626265256</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2462771507452516</v>
+        <v>0.2504209529516437</v>
       </c>
       <c r="T60">
-        <v>1.397815417130496</v>
+        <v>1.42670783997321</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.039756314612055</v>
+        <v>4.954336716059309</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.125511490710174</v>
+        <v>0.1251347781073422</v>
       </c>
       <c r="C61">
-        <v>69.64619808314194</v>
+        <v>69.37607127784526</v>
       </c>
       <c r="D61">
-        <v>116.4329717092871</v>
+        <v>116.9858410671454</v>
       </c>
       <c r="E61">
-        <v>-19.64284268935511</v>
+        <v>-18.81984652620011</v>
       </c>
       <c r="F61">
-        <v>48.55677362614515</v>
+        <v>49.37976978930016</v>
       </c>
       <c r="G61">
         <v>1.77</v>
@@ -6271,28 +6271,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M61">
-        <v>2.685189581525827</v>
+        <v>2.730701269348299</v>
       </c>
       <c r="N61">
-        <v>10.61814375180751</v>
+        <v>10.57263206398504</v>
       </c>
       <c r="O61">
-        <v>3.185443125542252</v>
+        <v>3.171789619195511</v>
       </c>
       <c r="P61">
-        <v>7.432700626265256</v>
+        <v>7.400842444789525</v>
       </c>
       <c r="Q61">
-        <v>7.562700626265256</v>
+        <v>7.530842444789525</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2504209529516437</v>
+        <v>0.2547719452683555</v>
       </c>
       <c r="T61">
-        <v>1.42670783997321</v>
+        <v>1.45704488395806</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.954336716059309</v>
+        <v>4.871764437458321</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1251347781073422</v>
+        <v>0.1247580655045105</v>
       </c>
       <c r="C62">
-        <v>69.37607127784526</v>
+        <v>69.11122000338878</v>
       </c>
       <c r="D62">
-        <v>116.9858410671454</v>
+        <v>117.5439859558439</v>
       </c>
       <c r="E62">
-        <v>-18.81984652620011</v>
+        <v>-17.99685036304511</v>
       </c>
       <c r="F62">
-        <v>49.37976978930016</v>
+        <v>50.20276595245516</v>
       </c>
       <c r="G62">
         <v>1.77</v>
@@ -6353,28 +6353,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M62">
-        <v>2.730701269348299</v>
+        <v>2.77621295717077</v>
       </c>
       <c r="N62">
-        <v>10.57263206398504</v>
+        <v>10.52712037616256</v>
       </c>
       <c r="O62">
-        <v>3.171789619195511</v>
+        <v>3.158136112848769</v>
       </c>
       <c r="P62">
-        <v>7.400842444789525</v>
+        <v>7.368984263313795</v>
       </c>
       <c r="Q62">
-        <v>7.530842444789525</v>
+        <v>7.498984263313795</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2547719452683555</v>
+        <v>0.2593460653961807</v>
       </c>
       <c r="T62">
-        <v>1.45704488395806</v>
+        <v>1.488937673788286</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.871764437458321</v>
+        <v>4.791899446680315</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1247580655045105</v>
+        <v>0.1243813529016787</v>
       </c>
       <c r="C63">
-        <v>69.11122000338878</v>
+        <v>68.8517201311674</v>
       </c>
       <c r="D63">
-        <v>117.5439859558439</v>
+        <v>118.1074822467776</v>
       </c>
       <c r="E63">
-        <v>-17.99685036304511</v>
+        <v>-17.1738541998901</v>
       </c>
       <c r="F63">
-        <v>50.20276595245516</v>
+        <v>51.02576211561016</v>
       </c>
       <c r="G63">
         <v>1.77</v>
@@ -6435,28 +6435,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M63">
-        <v>2.77621295717077</v>
+        <v>2.821724644993242</v>
       </c>
       <c r="N63">
-        <v>10.52712037616256</v>
+        <v>10.48160868834009</v>
       </c>
       <c r="O63">
-        <v>3.158136112848769</v>
+        <v>3.144482606502028</v>
       </c>
       <c r="P63">
-        <v>7.368984263313795</v>
+        <v>7.337126081838065</v>
       </c>
       <c r="Q63">
-        <v>7.498984263313795</v>
+        <v>7.467126081838065</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2593460653961807</v>
+        <v>0.2641609286886282</v>
       </c>
       <c r="T63">
-        <v>1.488937673788286</v>
+        <v>1.522509031504314</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.791899446680315</v>
+        <v>4.714610745927406</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1243813529016787</v>
+        <v>0.124004640298847</v>
       </c>
       <c r="C64">
-        <v>68.8517201311674</v>
+        <v>68.59764899446948</v>
       </c>
       <c r="D64">
-        <v>118.1074822467776</v>
+        <v>118.6764072732346</v>
       </c>
       <c r="E64">
-        <v>-17.1738541998901</v>
+        <v>-16.3508580367351</v>
       </c>
       <c r="F64">
-        <v>51.02576211561016</v>
+        <v>51.84875827876516</v>
       </c>
       <c r="G64">
         <v>1.77</v>
@@ -6517,28 +6517,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M64">
-        <v>2.821724644993242</v>
+        <v>2.867236332815713</v>
       </c>
       <c r="N64">
-        <v>10.48160868834009</v>
+        <v>10.43609700051762</v>
       </c>
       <c r="O64">
-        <v>3.144482606502028</v>
+        <v>3.130829100155287</v>
       </c>
       <c r="P64">
-        <v>7.337126081838065</v>
+        <v>7.305267900362335</v>
       </c>
       <c r="Q64">
-        <v>7.467126081838065</v>
+        <v>7.435267900362335</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2641609286886282</v>
+        <v>0.2692360548617486</v>
       </c>
       <c r="T64">
-        <v>1.522509031504314</v>
+        <v>1.557895057204992</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.714610745927406</v>
+        <v>4.63977565472221</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.124004640298847</v>
+        <v>0.1236279276960152</v>
       </c>
       <c r="C65">
-        <v>68.59764899446948</v>
+        <v>68.34908542385682</v>
       </c>
       <c r="D65">
-        <v>118.6764072732346</v>
+        <v>119.250839865777</v>
       </c>
       <c r="E65">
-        <v>-16.3508580367351</v>
+        <v>-15.5278618735801</v>
       </c>
       <c r="F65">
-        <v>51.84875827876516</v>
+        <v>52.67175444192016</v>
       </c>
       <c r="G65">
         <v>1.77</v>
@@ -6599,28 +6599,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M65">
-        <v>2.867236332815713</v>
+        <v>2.912748020638185</v>
       </c>
       <c r="N65">
-        <v>10.43609700051762</v>
+        <v>10.39058531269515</v>
       </c>
       <c r="O65">
-        <v>3.130829100155287</v>
+        <v>3.117175593808545</v>
       </c>
       <c r="P65">
-        <v>7.305267900362335</v>
+        <v>7.273409718886604</v>
       </c>
       <c r="Q65">
-        <v>7.435267900362335</v>
+        <v>7.403409718886604</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2692360548617486</v>
+        <v>0.2745931324889312</v>
       </c>
       <c r="T65">
-        <v>1.557895057204992</v>
+        <v>1.595246973222374</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.63977565472221</v>
+        <v>4.567279160117176</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1236279276960152</v>
+        <v>0.1243887150931835</v>
       </c>
       <c r="C66">
-        <v>68.34908542385682</v>
+        <v>66.37166733175134</v>
       </c>
       <c r="D66">
-        <v>119.250839865777</v>
+        <v>118.0964179368265</v>
       </c>
       <c r="E66">
-        <v>-15.5278618735801</v>
+        <v>-14.7048657104251</v>
       </c>
       <c r="F66">
-        <v>52.67175444192016</v>
+        <v>53.49475060507517</v>
       </c>
       <c r="G66">
         <v>1.77</v>
@@ -6681,45 +6681,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M66">
-        <v>2.912748020638185</v>
+        <v>3.091996584973345</v>
       </c>
       <c r="N66">
-        <v>10.39058531269515</v>
+        <v>10.21133674835999</v>
       </c>
       <c r="O66">
-        <v>3.117175593808545</v>
+        <v>3.063401024507997</v>
       </c>
       <c r="P66">
-        <v>7.273409718886604</v>
+        <v>7.147935723851994</v>
       </c>
       <c r="Q66">
-        <v>7.403409718886604</v>
+        <v>7.277935723851994</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2745931324889312</v>
+        <v>0.2802563288376672</v>
       </c>
       <c r="T66">
-        <v>1.595246973222374</v>
+        <v>1.63473328444075</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.567279160117176</v>
+        <v>4.302505830047034</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1243887150931835</v>
+        <v>0.1240295024903518</v>
       </c>
       <c r="C67">
-        <v>66.37166733175134</v>
+        <v>66.09094384478291</v>
       </c>
       <c r="D67">
-        <v>118.0964179368265</v>
+        <v>118.6386906130131</v>
       </c>
       <c r="E67">
-        <v>-14.7048657104251</v>
+        <v>-13.88186954727009</v>
       </c>
       <c r="F67">
-        <v>53.49475060507517</v>
+        <v>54.31774676823017</v>
       </c>
       <c r="G67">
         <v>1.77</v>
@@ -6763,28 +6763,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M67">
-        <v>3.091996584973345</v>
+        <v>3.139565763203704</v>
       </c>
       <c r="N67">
-        <v>10.21133674835999</v>
+        <v>10.16376757012963</v>
       </c>
       <c r="O67">
-        <v>3.063401024507997</v>
+        <v>3.049130271038889</v>
       </c>
       <c r="P67">
-        <v>7.147935723851994</v>
+        <v>7.114637299090742</v>
       </c>
       <c r="Q67">
-        <v>7.277935723851994</v>
+        <v>7.244637299090742</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2802563288376672</v>
+        <v>0.2862526543833876</v>
       </c>
       <c r="T67">
-        <v>1.63473328444075</v>
+        <v>1.676542319848442</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.302505830047034</v>
+        <v>4.237316347773593</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1240295024903518</v>
+        <v>0.12367028988752</v>
       </c>
       <c r="C68">
-        <v>66.09094384478291</v>
+        <v>65.81522332312366</v>
       </c>
       <c r="D68">
-        <v>118.6386906130131</v>
+        <v>119.1859662545088</v>
       </c>
       <c r="E68">
-        <v>-13.88186954727009</v>
+        <v>-13.05887338411509</v>
       </c>
       <c r="F68">
-        <v>54.31774676823017</v>
+        <v>55.14074293138518</v>
       </c>
       <c r="G68">
         <v>1.77</v>
@@ -6845,28 +6845,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M68">
-        <v>3.139565763203704</v>
+        <v>3.187134941434064</v>
       </c>
       <c r="N68">
-        <v>10.16376757012963</v>
+        <v>10.11619839189927</v>
       </c>
       <c r="O68">
-        <v>3.049130271038889</v>
+        <v>3.034859517569781</v>
       </c>
       <c r="P68">
-        <v>7.114637299090742</v>
+        <v>7.081338874329489</v>
       </c>
       <c r="Q68">
-        <v>7.244637299090742</v>
+        <v>7.211338874329489</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2862526543833876</v>
+        <v>0.2926123935985456</v>
       </c>
       <c r="T68">
-        <v>1.676542319848442</v>
+        <v>1.720885236189933</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.237316347773593</v>
+        <v>4.174072820194883</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.12367028988752</v>
+        <v>0.1233110772846883</v>
       </c>
       <c r="C69">
-        <v>65.81522332312366</v>
+        <v>65.54457532308408</v>
       </c>
       <c r="D69">
-        <v>119.1859662545088</v>
+        <v>119.7383144176243</v>
       </c>
       <c r="E69">
-        <v>-13.05887338411509</v>
+        <v>-12.23587722096008</v>
       </c>
       <c r="F69">
-        <v>55.14074293138518</v>
+        <v>55.96373909454018</v>
       </c>
       <c r="G69">
         <v>1.77</v>
@@ -6927,28 +6927,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M69">
-        <v>3.187134941434064</v>
+        <v>3.234704119664423</v>
       </c>
       <c r="N69">
-        <v>10.11619839189927</v>
+        <v>10.06862921366891</v>
       </c>
       <c r="O69">
-        <v>3.034859517569781</v>
+        <v>3.020588764100673</v>
       </c>
       <c r="P69">
-        <v>7.081338874329489</v>
+        <v>7.048040449568238</v>
       </c>
       <c r="Q69">
-        <v>7.211338874329489</v>
+        <v>7.178040449568238</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2926123935985456</v>
+        <v>0.299369616514651</v>
       </c>
       <c r="T69">
-        <v>1.720885236189933</v>
+        <v>1.767999584802768</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.174072820194883</v>
+        <v>4.112689396368488</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1233110772846883</v>
+        <v>0.1229518646818566</v>
       </c>
       <c r="C70">
-        <v>65.54457532308408</v>
+        <v>65.27907069636834</v>
       </c>
       <c r="D70">
-        <v>119.7383144176243</v>
+        <v>120.2958059540635</v>
       </c>
       <c r="E70">
-        <v>-12.23587722096008</v>
+        <v>-11.41288105780508</v>
       </c>
       <c r="F70">
-        <v>55.96373909454018</v>
+        <v>56.78673525769518</v>
       </c>
       <c r="G70">
         <v>1.77</v>
@@ -7009,28 +7009,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M70">
-        <v>3.234704119664423</v>
+        <v>3.282273297894782</v>
       </c>
       <c r="N70">
-        <v>10.06862921366891</v>
+        <v>10.02106003543855</v>
       </c>
       <c r="O70">
-        <v>3.020588764100673</v>
+        <v>3.006318010631566</v>
       </c>
       <c r="P70">
-        <v>7.048040449568238</v>
+        <v>7.014742024806987</v>
       </c>
       <c r="Q70">
-        <v>7.178040449568238</v>
+        <v>7.144742024806987</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.299369616514651</v>
+        <v>0.3065627892963115</v>
       </c>
       <c r="T70">
-        <v>1.767999584802768</v>
+        <v>1.818153568809979</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.112689396368488</v>
+        <v>4.053085202218219</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1229518646818566</v>
+        <v>0.1243076520790248</v>
       </c>
       <c r="C71">
-        <v>65.27907069636834</v>
+        <v>62.37862687905923</v>
       </c>
       <c r="D71">
-        <v>120.2958059540635</v>
+        <v>118.2183582999094</v>
       </c>
       <c r="E71">
-        <v>-11.41288105780508</v>
+        <v>-10.58988489465008</v>
       </c>
       <c r="F71">
-        <v>56.78673525769518</v>
+        <v>57.60973142085019</v>
       </c>
       <c r="G71">
         <v>1.77</v>
@@ -7091,45 +7091,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M71">
-        <v>3.282273297894782</v>
+        <v>3.531476536098117</v>
       </c>
       <c r="N71">
-        <v>10.02106003543855</v>
+        <v>9.771856797235218</v>
       </c>
       <c r="O71">
-        <v>3.006318010631566</v>
+        <v>2.931557039170565</v>
       </c>
       <c r="P71">
-        <v>7.014742024806987</v>
+        <v>6.840299758064653</v>
       </c>
       <c r="Q71">
-        <v>7.144742024806987</v>
+        <v>6.970299758064653</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3065627892963115</v>
+        <v>0.3142355069300828</v>
       </c>
       <c r="T71">
-        <v>1.818153568809979</v>
+        <v>1.871651151751004</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.3</v>
       </c>
       <c r="W71">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.053085202218219</v>
+        <v>3.76707396958441</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1243076520790248</v>
+        <v>0.1239729394761931</v>
       </c>
       <c r="C72">
-        <v>62.37862687905923</v>
+        <v>62.0618055466602</v>
       </c>
       <c r="D72">
-        <v>118.2183582999094</v>
+        <v>118.7245331306654</v>
       </c>
       <c r="E72">
-        <v>-10.58988489465008</v>
+        <v>-9.766888731495072</v>
       </c>
       <c r="F72">
-        <v>57.60973142085019</v>
+        <v>58.43272758400519</v>
       </c>
       <c r="G72">
         <v>1.77</v>
@@ -7173,28 +7173,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M72">
-        <v>3.531476536098117</v>
+        <v>3.581926200899519</v>
       </c>
       <c r="N72">
-        <v>9.771856797235218</v>
+        <v>9.721407132433816</v>
       </c>
       <c r="O72">
-        <v>2.931557039170565</v>
+        <v>2.916422139730145</v>
       </c>
       <c r="P72">
-        <v>6.840299758064653</v>
+        <v>6.804984992703671</v>
       </c>
       <c r="Q72">
-        <v>6.970299758064653</v>
+        <v>6.934984992703671</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3142355069300828</v>
+        <v>0.3224373775041141</v>
       </c>
       <c r="T72">
-        <v>1.871651151751004</v>
+        <v>1.92883822317072</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.76707396958441</v>
+        <v>3.714016589731108</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1239729394761931</v>
+        <v>0.1236382268733613</v>
       </c>
       <c r="C73">
-        <v>62.06180554666018</v>
+        <v>61.7493374248081</v>
       </c>
       <c r="D73">
-        <v>118.7245331306654</v>
+        <v>119.2350611719683</v>
       </c>
       <c r="E73">
-        <v>-9.766888731495087</v>
+        <v>-8.943892568340083</v>
       </c>
       <c r="F73">
-        <v>58.43272758400518</v>
+        <v>59.25572374716018</v>
       </c>
       <c r="G73">
         <v>1.77</v>
@@ -7255,28 +7255,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M73">
-        <v>3.581926200899518</v>
+        <v>3.632375865700919</v>
       </c>
       <c r="N73">
-        <v>9.721407132433818</v>
+        <v>9.670957467632416</v>
       </c>
       <c r="O73">
-        <v>2.916422139730145</v>
+        <v>2.901287240289725</v>
       </c>
       <c r="P73">
-        <v>6.804984992703673</v>
+        <v>6.769670227342692</v>
       </c>
       <c r="Q73">
-        <v>6.934984992703673</v>
+        <v>6.899670227342692</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3224373775041141</v>
+        <v>0.3312250959762905</v>
       </c>
       <c r="T73">
-        <v>1.92883822317072</v>
+        <v>1.99011008540613</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.71401658973111</v>
+        <v>3.662433025984844</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1236382268733613</v>
+        <v>0.1233035142705296</v>
       </c>
       <c r="C74">
-        <v>61.7493374248081</v>
+        <v>61.44127891382669</v>
       </c>
       <c r="D74">
-        <v>119.2350611719683</v>
+        <v>119.7499988241419</v>
       </c>
       <c r="E74">
-        <v>-8.943892568340083</v>
+        <v>-8.120896405185078</v>
       </c>
       <c r="F74">
-        <v>59.25572374716018</v>
+        <v>60.07871991031519</v>
       </c>
       <c r="G74">
         <v>1.77</v>
@@ -7337,28 +7337,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M74">
-        <v>3.632375865700919</v>
+        <v>3.682825530502321</v>
       </c>
       <c r="N74">
-        <v>9.670957467632416</v>
+        <v>9.620507802831014</v>
       </c>
       <c r="O74">
-        <v>2.901287240289725</v>
+        <v>2.886152340849304</v>
       </c>
       <c r="P74">
-        <v>6.769670227342692</v>
+        <v>6.734355461981711</v>
       </c>
       <c r="Q74">
-        <v>6.899670227342692</v>
+        <v>6.86435546198171</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3312250959762905</v>
+        <v>0.340663756557517</v>
       </c>
       <c r="T74">
-        <v>1.99011008540613</v>
+        <v>2.055920604103423</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.662433025984844</v>
+        <v>3.612262710560394</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1233035142705296</v>
+        <v>0.1229688016676979</v>
       </c>
       <c r="C75">
-        <v>61.44127891382669</v>
+        <v>61.13768739256475</v>
       </c>
       <c r="D75">
-        <v>119.7499988241419</v>
+        <v>120.2694034660349</v>
       </c>
       <c r="E75">
-        <v>-8.120896405185078</v>
+        <v>-7.297900242030074</v>
       </c>
       <c r="F75">
-        <v>60.07871991031519</v>
+        <v>60.90171607347019</v>
       </c>
       <c r="G75">
         <v>1.77</v>
@@ -7419,28 +7419,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M75">
-        <v>3.682825530502321</v>
+        <v>3.733275195303723</v>
       </c>
       <c r="N75">
-        <v>9.620507802831014</v>
+        <v>9.570058138029612</v>
       </c>
       <c r="O75">
-        <v>2.886152340849304</v>
+        <v>2.871017441408883</v>
       </c>
       <c r="P75">
-        <v>6.734355461981711</v>
+        <v>6.699040696620729</v>
       </c>
       <c r="Q75">
-        <v>6.86435546198171</v>
+        <v>6.829040696620729</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.340663756557517</v>
+        <v>0.3508284679526841</v>
       </c>
       <c r="T75">
-        <v>2.055920604103423</v>
+        <v>2.126793470392815</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.612262710560394</v>
+        <v>3.563448349606875</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1229688016676979</v>
+        <v>0.1226340890648661</v>
       </c>
       <c r="C76">
-        <v>61.13768739256475</v>
+        <v>60.83862123970962</v>
       </c>
       <c r="D76">
-        <v>120.2694034660349</v>
+        <v>120.7933334763348</v>
       </c>
       <c r="E76">
-        <v>-7.297900242030074</v>
+        <v>-6.47490407887507</v>
       </c>
       <c r="F76">
-        <v>60.90171607347019</v>
+        <v>61.72471223662519</v>
       </c>
       <c r="G76">
         <v>1.77</v>
@@ -7501,28 +7501,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M76">
-        <v>3.733275195303723</v>
+        <v>3.783724860105124</v>
       </c>
       <c r="N76">
-        <v>9.570058138029612</v>
+        <v>9.51960847322821</v>
       </c>
       <c r="O76">
-        <v>2.871017441408883</v>
+        <v>2.855882541968463</v>
       </c>
       <c r="P76">
-        <v>6.699040696620729</v>
+        <v>6.663725931259748</v>
       </c>
       <c r="Q76">
-        <v>6.829040696620729</v>
+        <v>6.793725931259748</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3508284679526841</v>
+        <v>0.3618063562594644</v>
       </c>
       <c r="T76">
-        <v>2.126793470392815</v>
+        <v>2.203336165985359</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.563448349606875</v>
+        <v>3.51593570494545</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1226340890648661</v>
+        <v>0.1237889764620344</v>
       </c>
       <c r="C77">
-        <v>60.83862123970962</v>
+        <v>58.22687614276558</v>
       </c>
       <c r="D77">
-        <v>120.7933334763348</v>
+        <v>119.0045845425458</v>
       </c>
       <c r="E77">
-        <v>-6.47490407887507</v>
+        <v>-5.651907915720066</v>
       </c>
       <c r="F77">
-        <v>61.72471223662519</v>
+        <v>62.5477083997802</v>
       </c>
       <c r="G77">
         <v>1.77</v>
@@ -7583,45 +7583,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M77">
-        <v>3.783724860105124</v>
+        <v>4.009308108425911</v>
       </c>
       <c r="N77">
-        <v>9.51960847322821</v>
+        <v>9.294025224907424</v>
       </c>
       <c r="O77">
-        <v>2.855882541968463</v>
+        <v>2.788207567472227</v>
       </c>
       <c r="P77">
-        <v>6.663725931259748</v>
+        <v>6.505817657435196</v>
       </c>
       <c r="Q77">
-        <v>6.793725931259748</v>
+        <v>6.635817657435196</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3618063562594644</v>
+        <v>0.37369906859181</v>
       </c>
       <c r="T77">
-        <v>2.203336165985359</v>
+        <v>2.286257419543948</v>
       </c>
       <c r="U77">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.3</v>
       </c>
       <c r="W77">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.51593570494545</v>
+        <v>3.318111996774511</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1237889764620344</v>
+        <v>0.1234738638592026</v>
       </c>
       <c r="C78">
-        <v>58.22687614276558</v>
+        <v>57.88666585533433</v>
       </c>
       <c r="D78">
-        <v>119.0045845425458</v>
+        <v>119.4873704182695</v>
       </c>
       <c r="E78">
-        <v>-5.651907915720066</v>
+        <v>-4.828911752565062</v>
       </c>
       <c r="F78">
-        <v>62.5477083997802</v>
+        <v>63.3707045629352</v>
       </c>
       <c r="G78">
         <v>1.77</v>
@@ -7665,28 +7665,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M78">
-        <v>4.009308108425911</v>
+        <v>4.062062162484147</v>
       </c>
       <c r="N78">
-        <v>9.294025224907424</v>
+        <v>9.241271170849188</v>
       </c>
       <c r="O78">
-        <v>2.788207567472227</v>
+        <v>2.772381351254757</v>
       </c>
       <c r="P78">
-        <v>6.505817657435196</v>
+        <v>6.468889819594432</v>
       </c>
       <c r="Q78">
-        <v>6.635817657435196</v>
+        <v>6.598889819594432</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.37369906859181</v>
+        <v>0.3866259298226202</v>
       </c>
       <c r="T78">
-        <v>2.286257419543948</v>
+        <v>2.37638921689024</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.318111996774511</v>
+        <v>3.275019633180036</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1234738638592026</v>
+        <v>0.1231587512563709</v>
       </c>
       <c r="C79">
-        <v>57.88666585533433</v>
+        <v>57.55038872120346</v>
       </c>
       <c r="D79">
-        <v>119.4873704182695</v>
+        <v>119.9740894472937</v>
       </c>
       <c r="E79">
-        <v>-4.828911752565062</v>
+        <v>-4.005915589410066</v>
       </c>
       <c r="F79">
-        <v>63.3707045629352</v>
+        <v>64.1937007260902</v>
       </c>
       <c r="G79">
         <v>1.77</v>
@@ -7747,28 +7747,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M79">
-        <v>4.062062162484147</v>
+        <v>4.114816216542382</v>
       </c>
       <c r="N79">
-        <v>9.241271170849188</v>
+        <v>9.188517116790953</v>
       </c>
       <c r="O79">
-        <v>2.772381351254757</v>
+        <v>2.756555135037286</v>
       </c>
       <c r="P79">
-        <v>6.468889819594432</v>
+        <v>6.431961981753667</v>
       </c>
       <c r="Q79">
-        <v>6.598889819594432</v>
+        <v>6.561961981753667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3866259298226202</v>
+        <v>0.4007279602562314</v>
       </c>
       <c r="T79">
-        <v>2.37638921689024</v>
+        <v>2.474714813995285</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.275019633180036</v>
+        <v>3.233032201985421</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1231587512563709</v>
+        <v>0.1228436386535392</v>
       </c>
       <c r="C80">
-        <v>57.55038872120346</v>
+        <v>57.21809300079511</v>
       </c>
       <c r="D80">
-        <v>119.9740894472937</v>
+        <v>120.4647898900403</v>
       </c>
       <c r="E80">
-        <v>-4.005915589410066</v>
+        <v>-3.182919426255054</v>
       </c>
       <c r="F80">
-        <v>64.1937007260902</v>
+        <v>65.01669688924521</v>
       </c>
       <c r="G80">
         <v>1.77</v>
@@ -7829,28 +7829,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M80">
-        <v>4.114816216542382</v>
+        <v>4.167570270600618</v>
       </c>
       <c r="N80">
-        <v>9.188517116790953</v>
+        <v>9.135763062732718</v>
       </c>
       <c r="O80">
-        <v>2.756555135037286</v>
+        <v>2.740728918819815</v>
       </c>
       <c r="P80">
-        <v>6.431961981753667</v>
+        <v>6.395034143912902</v>
       </c>
       <c r="Q80">
-        <v>6.561961981753667</v>
+        <v>6.525034143912902</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4007279602562314</v>
+        <v>0.4161730412073294</v>
       </c>
       <c r="T80">
-        <v>2.474714813995285</v>
+        <v>2.582404753681765</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.233032201985421</v>
+        <v>3.192107743732441</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1228436386535392</v>
+        <v>0.1225285260507074</v>
       </c>
       <c r="C81">
-        <v>57.21809300079511</v>
+        <v>56.88982774732479</v>
       </c>
       <c r="D81">
-        <v>120.4647898900403</v>
+        <v>120.959520799725</v>
       </c>
       <c r="E81">
-        <v>-3.182919426255054</v>
+        <v>-2.359923263100058</v>
       </c>
       <c r="F81">
-        <v>65.01669688924521</v>
+        <v>65.83969305240021</v>
       </c>
       <c r="G81">
         <v>1.77</v>
@@ -7911,28 +7911,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M81">
-        <v>4.167570270600618</v>
+        <v>4.220324324658853</v>
       </c>
       <c r="N81">
-        <v>9.135763062732718</v>
+        <v>9.08300900867448</v>
       </c>
       <c r="O81">
-        <v>2.740728918819815</v>
+        <v>2.724902702602344</v>
       </c>
       <c r="P81">
-        <v>6.395034143912902</v>
+        <v>6.358106306072136</v>
       </c>
       <c r="Q81">
-        <v>6.525034143912902</v>
+        <v>6.488106306072136</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4161730412073294</v>
+        <v>0.4331626302535371</v>
       </c>
       <c r="T81">
-        <v>2.582404753681765</v>
+        <v>2.700863687336891</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.192107743732441</v>
+        <v>3.152206396935785</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1225285260507074</v>
+        <v>0.1222134134478757</v>
       </c>
       <c r="C82">
-        <v>56.88982774732479</v>
+        <v>56.56564282314787</v>
       </c>
       <c r="D82">
-        <v>120.959520799725</v>
+        <v>121.4583320387031</v>
       </c>
       <c r="E82">
-        <v>-2.359923263100058</v>
+        <v>-1.536927099945046</v>
       </c>
       <c r="F82">
-        <v>65.83969305240021</v>
+        <v>66.66268921555522</v>
       </c>
       <c r="G82">
         <v>1.77</v>
@@ -7993,28 +7993,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M82">
-        <v>4.220324324658853</v>
+        <v>4.27307837871709</v>
       </c>
       <c r="N82">
-        <v>9.08300900867448</v>
+        <v>9.030254954616245</v>
       </c>
       <c r="O82">
-        <v>2.724902702602344</v>
+        <v>2.709076486384873</v>
       </c>
       <c r="P82">
-        <v>6.358106306072136</v>
+        <v>6.321178468231372</v>
       </c>
       <c r="Q82">
-        <v>6.488106306072136</v>
+        <v>6.451178468231372</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4331626302535371</v>
+        <v>0.4519405970940826</v>
       </c>
       <c r="T82">
-        <v>2.700863687336891</v>
+        <v>2.8317919824294</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.152206396935785</v>
+        <v>3.113290268578553</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1222134134478757</v>
+        <v>0.1218983008450439</v>
       </c>
       <c r="C83">
-        <v>56.56564282314787</v>
+        <v>56.2455889165125</v>
       </c>
       <c r="D83">
-        <v>121.4583320387031</v>
+        <v>121.9612742952227</v>
       </c>
       <c r="E83">
-        <v>-1.536927099945046</v>
+        <v>-0.7139309367900495</v>
       </c>
       <c r="F83">
-        <v>66.66268921555522</v>
+        <v>67.48568537871022</v>
       </c>
       <c r="G83">
         <v>1.77</v>
@@ -8075,28 +8075,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M83">
-        <v>4.27307837871709</v>
+        <v>4.325832432775325</v>
       </c>
       <c r="N83">
-        <v>9.030254954616245</v>
+        <v>8.97750090055801</v>
       </c>
       <c r="O83">
-        <v>2.709076486384873</v>
+        <v>2.693250270167403</v>
       </c>
       <c r="P83">
-        <v>6.321178468231372</v>
+        <v>6.284250630390607</v>
       </c>
       <c r="Q83">
-        <v>6.451178468231372</v>
+        <v>6.414250630390607</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4519405970940826</v>
+        <v>0.4728050046946887</v>
       </c>
       <c r="T83">
-        <v>2.8317919824294</v>
+        <v>2.977267865865521</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.113290268578553</v>
+        <v>3.075323314083692</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1218983008450439</v>
+        <v>0.1215831882422122</v>
       </c>
       <c r="C84">
-        <v>56.2455889165125</v>
+        <v>55.92971755873006</v>
       </c>
       <c r="D84">
-        <v>121.9612742952227</v>
+        <v>122.4683991005953</v>
       </c>
       <c r="E84">
-        <v>-0.7139309367900495</v>
+        <v>0.1090652263649616</v>
       </c>
       <c r="F84">
-        <v>67.48568537871022</v>
+        <v>68.30868154186523</v>
       </c>
       <c r="G84">
         <v>1.77</v>
@@ -8157,28 +8157,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M84">
-        <v>4.325832432775325</v>
+        <v>4.378586486833561</v>
       </c>
       <c r="N84">
-        <v>8.97750090055801</v>
+        <v>8.924746846499772</v>
       </c>
       <c r="O84">
-        <v>2.693250270167403</v>
+        <v>2.677424053949931</v>
       </c>
       <c r="P84">
-        <v>6.284250630390607</v>
+        <v>6.247322792549841</v>
       </c>
       <c r="Q84">
-        <v>6.414250630390607</v>
+        <v>6.377322792549841</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4728050046946887</v>
+        <v>0.4961240484836014</v>
       </c>
       <c r="T84">
-        <v>2.977267865865521</v>
+        <v>3.139858559117656</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.075323314083692</v>
+        <v>3.038271225962202</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1215831882422122</v>
+        <v>0.1212680756393805</v>
       </c>
       <c r="C85">
-        <v>55.92971755873006</v>
+        <v>55.61808114177597</v>
       </c>
       <c r="D85">
-        <v>122.4683991005953</v>
+        <v>122.9797588467962</v>
       </c>
       <c r="E85">
-        <v>0.1090652263649616</v>
+        <v>0.9320613895199585</v>
       </c>
       <c r="F85">
-        <v>68.30868154186523</v>
+        <v>69.13167770502022</v>
       </c>
       <c r="G85">
         <v>1.77</v>
@@ -8239,28 +8239,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M85">
-        <v>4.378586486833561</v>
+        <v>4.431340540891797</v>
       </c>
       <c r="N85">
-        <v>8.924746846499772</v>
+        <v>8.871992792441539</v>
       </c>
       <c r="O85">
-        <v>2.677424053949931</v>
+        <v>2.661597837732462</v>
       </c>
       <c r="P85">
-        <v>6.247322792549841</v>
+        <v>6.210394954709077</v>
       </c>
       <c r="Q85">
-        <v>6.377322792549841</v>
+        <v>6.340394954709077</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4961240484836014</v>
+        <v>0.5223579727461282</v>
       </c>
       <c r="T85">
-        <v>3.139858559117656</v>
+        <v>3.322773089026309</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.038271225962202</v>
+        <v>3.002101330415033</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1212680756393805</v>
+        <v>0.1255939630365487</v>
       </c>
       <c r="C86">
-        <v>55.61808114177599</v>
+        <v>48.12795668147811</v>
       </c>
       <c r="D86">
-        <v>122.9797588467962</v>
+        <v>116.3126305496533</v>
       </c>
       <c r="E86">
-        <v>0.9320613895199443</v>
+        <v>1.755057552674955</v>
       </c>
       <c r="F86">
-        <v>69.13167770502021</v>
+        <v>69.95467386817522</v>
       </c>
       <c r="G86">
         <v>1.77</v>
@@ -8321,45 +8321,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M86">
-        <v>4.431340540891796</v>
+        <v>5.029741051121799</v>
       </c>
       <c r="N86">
-        <v>8.871992792441539</v>
+        <v>8.273592282211535</v>
       </c>
       <c r="O86">
-        <v>2.661597837732462</v>
+        <v>2.48207768466346</v>
       </c>
       <c r="P86">
-        <v>6.210394954709077</v>
+        <v>5.791514597548074</v>
       </c>
       <c r="Q86">
-        <v>6.340394954709077</v>
+        <v>5.921514597548074</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5223579727461278</v>
+        <v>0.5520897535769913</v>
       </c>
       <c r="T86">
-        <v>3.322773089026307</v>
+        <v>3.530076222922778</v>
       </c>
       <c r="U86">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V86">
         <v>0.3</v>
       </c>
       <c r="W86">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.002101330415034</v>
+        <v>2.644934042949636</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1255939630365487</v>
+        <v>0.125333450433717</v>
       </c>
       <c r="C87">
-        <v>48.12795668147811</v>
+        <v>47.68594368907024</v>
       </c>
       <c r="D87">
-        <v>116.3126305496533</v>
+        <v>116.6936137204005</v>
       </c>
       <c r="E87">
-        <v>1.755057552674955</v>
+        <v>2.578053715829952</v>
       </c>
       <c r="F87">
-        <v>69.95467386817522</v>
+        <v>70.77767003133022</v>
       </c>
       <c r="G87">
         <v>1.77</v>
@@ -8403,28 +8403,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M87">
-        <v>5.029741051121799</v>
+        <v>5.088914475252643</v>
       </c>
       <c r="N87">
-        <v>8.273592282211535</v>
+        <v>8.214418858080691</v>
       </c>
       <c r="O87">
-        <v>2.48207768466346</v>
+        <v>2.464325657424207</v>
       </c>
       <c r="P87">
-        <v>5.791514597548074</v>
+        <v>5.750093200656484</v>
       </c>
       <c r="Q87">
-        <v>5.921514597548074</v>
+        <v>5.880093200656484</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5520897535769913</v>
+        <v>0.5860689316694069</v>
       </c>
       <c r="T87">
-        <v>3.530076222922778</v>
+        <v>3.766994090233032</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.644934042949636</v>
+        <v>2.614178995938595</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.125333450433717</v>
+        <v>0.1250729378308852</v>
       </c>
       <c r="C88">
-        <v>47.68594368907024</v>
+        <v>47.24643472691936</v>
       </c>
       <c r="D88">
-        <v>116.6936137204005</v>
+        <v>117.0771009214046</v>
       </c>
       <c r="E88">
-        <v>2.578053715829952</v>
+        <v>3.401049878984963</v>
       </c>
       <c r="F88">
-        <v>70.77767003133022</v>
+        <v>71.60066619448523</v>
       </c>
       <c r="G88">
         <v>1.77</v>
@@ -8485,28 +8485,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M88">
-        <v>5.088914475252643</v>
+        <v>5.148087899383488</v>
       </c>
       <c r="N88">
-        <v>8.214418858080691</v>
+        <v>8.155245433949847</v>
       </c>
       <c r="O88">
-        <v>2.464325657424207</v>
+        <v>2.446573630184954</v>
       </c>
       <c r="P88">
-        <v>5.750093200656484</v>
+        <v>5.708671803764894</v>
       </c>
       <c r="Q88">
-        <v>5.880093200656484</v>
+        <v>5.838671803764893</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5860689316694069</v>
+        <v>0.6252756756221941</v>
       </c>
       <c r="T88">
-        <v>3.766994090233032</v>
+        <v>4.040360860206402</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.614178995938595</v>
+        <v>2.584130961502519</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1250729378308852</v>
+        <v>0.1248124252280535</v>
       </c>
       <c r="C89">
-        <v>47.24643472691936</v>
+        <v>46.80945456321</v>
       </c>
       <c r="D89">
-        <v>117.0771009214046</v>
+        <v>117.4631169208502</v>
       </c>
       <c r="E89">
-        <v>3.401049878984963</v>
+        <v>4.22404604213996</v>
       </c>
       <c r="F89">
-        <v>71.60066619448523</v>
+        <v>72.42366235764023</v>
       </c>
       <c r="G89">
         <v>1.77</v>
@@ -8567,28 +8567,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M89">
-        <v>5.148087899383488</v>
+        <v>5.207261323514333</v>
       </c>
       <c r="N89">
-        <v>8.155245433949847</v>
+        <v>8.096072009819002</v>
       </c>
       <c r="O89">
-        <v>2.446573630184954</v>
+        <v>2.428821602945701</v>
       </c>
       <c r="P89">
-        <v>5.708671803764894</v>
+        <v>5.667250406873301</v>
       </c>
       <c r="Q89">
-        <v>5.838671803764893</v>
+        <v>5.797250406873301</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6252756756221941</v>
+        <v>0.6710168769004459</v>
       </c>
       <c r="T89">
-        <v>4.040360860206402</v>
+        <v>4.359288758508667</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.584130961502519</v>
+        <v>2.55476583693999</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1248124252280535</v>
+        <v>0.1245519126252218</v>
       </c>
       <c r="C90">
-        <v>46.80945456321</v>
+        <v>46.37502829386071</v>
       </c>
       <c r="D90">
-        <v>117.4631169208502</v>
+        <v>117.8516868146559</v>
       </c>
       <c r="E90">
-        <v>4.22404604213996</v>
+        <v>5.047042205294971</v>
       </c>
       <c r="F90">
-        <v>72.42366235764023</v>
+        <v>73.24665852079524</v>
       </c>
       <c r="G90">
         <v>1.77</v>
@@ -8649,28 +8649,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M90">
-        <v>5.207261323514333</v>
+        <v>5.266434747645178</v>
       </c>
       <c r="N90">
-        <v>8.096072009819002</v>
+        <v>8.036898585688157</v>
       </c>
       <c r="O90">
-        <v>2.428821602945701</v>
+        <v>2.411069575706447</v>
       </c>
       <c r="P90">
-        <v>5.667250406873301</v>
+        <v>5.625829009981709</v>
       </c>
       <c r="Q90">
-        <v>5.797250406873301</v>
+        <v>5.755829009981709</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6710168769004459</v>
+        <v>0.7250746602292888</v>
       </c>
       <c r="T90">
-        <v>4.359288758508667</v>
+        <v>4.736203547411344</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.55476583693999</v>
+        <v>2.526060602817068</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1245519126252218</v>
+        <v>0.12674840002239</v>
       </c>
       <c r="C91">
-        <v>46.37502829386071</v>
+        <v>42.35419567251985</v>
       </c>
       <c r="D91">
-        <v>117.8516868146559</v>
+        <v>114.6538503564701</v>
       </c>
       <c r="E91">
-        <v>5.047042205294971</v>
+        <v>5.870038368449968</v>
       </c>
       <c r="F91">
-        <v>73.24665852079524</v>
+        <v>74.06965468395023</v>
       </c>
       <c r="G91">
         <v>1.77</v>
@@ -8731,45 +8731,45 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M91">
-        <v>5.266434747645178</v>
+        <v>5.614479825043428</v>
       </c>
       <c r="N91">
-        <v>8.036898585688157</v>
+        <v>7.688853508289906</v>
       </c>
       <c r="O91">
-        <v>2.411069575706447</v>
+        <v>2.306656052486972</v>
       </c>
       <c r="P91">
-        <v>5.625829009981709</v>
+        <v>5.382197455802935</v>
       </c>
       <c r="Q91">
-        <v>5.755829009981709</v>
+        <v>5.512197455802935</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7250746602292888</v>
+        <v>0.7899440002239002</v>
       </c>
       <c r="T91">
-        <v>4.736203547411344</v>
+        <v>5.188501294094555</v>
       </c>
       <c r="U91">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.3</v>
       </c>
       <c r="W91">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.526060602817068</v>
+        <v>2.369468543460379</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.12674840002239</v>
+        <v>0.1265151874195583</v>
       </c>
       <c r="C92">
-        <v>42.35419567251985</v>
+        <v>41.86247202103388</v>
       </c>
       <c r="D92">
-        <v>114.6538503564701</v>
+        <v>114.9851228681391</v>
       </c>
       <c r="E92">
-        <v>5.870038368449968</v>
+        <v>6.69303453160498</v>
       </c>
       <c r="F92">
-        <v>74.06965468395023</v>
+        <v>74.89265084710524</v>
       </c>
       <c r="G92">
         <v>1.77</v>
@@ -8813,28 +8813,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M92">
-        <v>5.614479825043428</v>
+        <v>5.676862934210578</v>
       </c>
       <c r="N92">
-        <v>7.688853508289906</v>
+        <v>7.626470399122756</v>
       </c>
       <c r="O92">
-        <v>2.306656052486972</v>
+        <v>2.287941119736827</v>
       </c>
       <c r="P92">
-        <v>5.382197455802935</v>
+        <v>5.33852927938593</v>
       </c>
       <c r="Q92">
-        <v>5.512197455802935</v>
+        <v>5.46852927938593</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7899440002239002</v>
+        <v>0.8692287491062032</v>
       </c>
       <c r="T92">
-        <v>5.188501294094555</v>
+        <v>5.741309651151814</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.369468543460379</v>
+        <v>2.343430427598177</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1265151874195583</v>
+        <v>0.1262819748167265</v>
       </c>
       <c r="C93">
-        <v>41.86247202103388</v>
+        <v>41.37266822613363</v>
       </c>
       <c r="D93">
-        <v>114.9851228681391</v>
+        <v>115.3183152363939</v>
       </c>
       <c r="E93">
-        <v>6.69303453160498</v>
+        <v>7.516030694759976</v>
       </c>
       <c r="F93">
-        <v>74.89265084710524</v>
+        <v>75.71564701026024</v>
       </c>
       <c r="G93">
         <v>1.77</v>
@@ -8895,28 +8895,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M93">
-        <v>5.676862934210578</v>
+        <v>5.739246043377727</v>
       </c>
       <c r="N93">
-        <v>7.626470399122756</v>
+        <v>7.564087289955608</v>
       </c>
       <c r="O93">
-        <v>2.287941119736827</v>
+        <v>2.269226186986682</v>
       </c>
       <c r="P93">
-        <v>5.33852927938593</v>
+        <v>5.294861102968925</v>
       </c>
       <c r="Q93">
-        <v>5.46852927938593</v>
+        <v>5.424861102968925</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8692287491062032</v>
+        <v>0.9683346852090823</v>
       </c>
       <c r="T93">
-        <v>5.741309651151814</v>
+        <v>6.432320097473389</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.343430427598177</v>
+        <v>2.317958357732979</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1262819748167265</v>
+        <v>0.1260487622138948</v>
       </c>
       <c r="C94">
-        <v>41.37266822613363</v>
+        <v>40.88480102582504</v>
       </c>
       <c r="D94">
-        <v>115.3183152363939</v>
+        <v>115.6534441992403</v>
       </c>
       <c r="E94">
-        <v>7.516030694759976</v>
+        <v>8.339026857914973</v>
       </c>
       <c r="F94">
-        <v>75.71564701026024</v>
+        <v>76.53864317341524</v>
       </c>
       <c r="G94">
         <v>1.77</v>
@@ -8977,28 +8977,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M94">
-        <v>5.739246043377727</v>
+        <v>5.801629152544876</v>
       </c>
       <c r="N94">
-        <v>7.564087289955608</v>
+        <v>7.501704180788459</v>
       </c>
       <c r="O94">
-        <v>2.269226186986682</v>
+        <v>2.250511254236538</v>
       </c>
       <c r="P94">
-        <v>5.294861102968925</v>
+        <v>5.251192926551921</v>
       </c>
       <c r="Q94">
-        <v>5.424861102968925</v>
+        <v>5.381192926551921</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9683346852090823</v>
+        <v>1.095756603055641</v>
       </c>
       <c r="T94">
-        <v>6.432320097473389</v>
+        <v>7.320762099886841</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.317958357732979</v>
+        <v>2.293034074316496</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1260487622138948</v>
+        <v>0.1258155496110631</v>
       </c>
       <c r="C95">
-        <v>40.88480102582504</v>
+        <v>40.39888735325172</v>
       </c>
       <c r="D95">
-        <v>115.6534441992403</v>
+        <v>115.990526689822</v>
       </c>
       <c r="E95">
-        <v>8.339026857914973</v>
+        <v>9.162023021069984</v>
       </c>
       <c r="F95">
-        <v>76.53864317341524</v>
+        <v>77.36163933657025</v>
       </c>
       <c r="G95">
         <v>1.77</v>
@@ -9059,28 +9059,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M95">
-        <v>5.801629152544876</v>
+        <v>5.864012261712025</v>
       </c>
       <c r="N95">
-        <v>7.501704180788459</v>
+        <v>7.439321071621309</v>
       </c>
       <c r="O95">
-        <v>2.250511254236538</v>
+        <v>2.231796321486393</v>
       </c>
       <c r="P95">
-        <v>5.251192926551921</v>
+        <v>5.207524750134917</v>
       </c>
       <c r="Q95">
-        <v>5.381192926551921</v>
+        <v>5.337524750134917</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.095756603055641</v>
+        <v>1.265652493517719</v>
       </c>
       <c r="T95">
-        <v>7.320762099886841</v>
+        <v>8.505351436438113</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.293034074316496</v>
+        <v>2.26864009480249</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1258155496110631</v>
+        <v>0.1255823370082313</v>
       </c>
       <c r="C96">
-        <v>40.39888735325172</v>
+        <v>39.91494433954712</v>
       </c>
       <c r="D96">
-        <v>115.990526689822</v>
+        <v>116.3295798392724</v>
       </c>
       <c r="E96">
-        <v>9.162023021069984</v>
+        <v>9.985019184224981</v>
       </c>
       <c r="F96">
-        <v>77.36163933657025</v>
+        <v>78.18463549972525</v>
       </c>
       <c r="G96">
         <v>1.77</v>
@@ -9141,28 +9141,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M96">
-        <v>5.864012261712025</v>
+        <v>5.926395370879174</v>
       </c>
       <c r="N96">
-        <v>7.439321071621309</v>
+        <v>7.376937962454161</v>
       </c>
       <c r="O96">
-        <v>2.231796321486393</v>
+        <v>2.213081388736248</v>
       </c>
       <c r="P96">
-        <v>5.207524750134917</v>
+        <v>5.163856573717913</v>
       </c>
       <c r="Q96">
-        <v>5.337524750134917</v>
+        <v>5.293856573717913</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.265652493517719</v>
+        <v>1.503506740164628</v>
       </c>
       <c r="T96">
-        <v>8.505351436438113</v>
+        <v>10.16377650760989</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.26864009480249</v>
+        <v>2.244759672751938</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1255823370082313</v>
+        <v>0.1253491244053996</v>
       </c>
       <c r="C97">
-        <v>39.91494433954712</v>
+        <v>39.43298931673684</v>
       </c>
       <c r="D97">
-        <v>116.3295798392724</v>
+        <v>116.6706209796171</v>
       </c>
       <c r="E97">
-        <v>9.985019184224981</v>
+        <v>10.80801534737999</v>
       </c>
       <c r="F97">
-        <v>78.18463549972525</v>
+        <v>79.00763166288026</v>
       </c>
       <c r="G97">
         <v>1.77</v>
@@ -9223,28 +9223,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M97">
-        <v>5.926395370879174</v>
+        <v>5.988778480046324</v>
       </c>
       <c r="N97">
-        <v>7.376937962454161</v>
+        <v>7.31455485328701</v>
       </c>
       <c r="O97">
-        <v>2.213081388736248</v>
+        <v>2.194366455986103</v>
       </c>
       <c r="P97">
-        <v>5.163856573717913</v>
+        <v>5.120188397300907</v>
       </c>
       <c r="Q97">
-        <v>5.293856573717913</v>
+        <v>5.250188397300907</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.503506740164628</v>
+        <v>1.860288110134993</v>
       </c>
       <c r="T97">
-        <v>10.16377650760989</v>
+        <v>12.65141411436757</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.244759672751938</v>
+        <v>2.221376759494105</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1253491244053996</v>
+        <v>0.1251159118025678</v>
       </c>
       <c r="C98">
-        <v>39.43298931673685</v>
+        <v>38.95303982069173</v>
       </c>
       <c r="D98">
-        <v>116.6706209796171</v>
+        <v>117.013667646727</v>
       </c>
       <c r="E98">
-        <v>10.80801534737998</v>
+        <v>11.63101151053499</v>
       </c>
       <c r="F98">
-        <v>79.00763166288024</v>
+        <v>79.83062782603525</v>
       </c>
       <c r="G98">
         <v>1.77</v>
@@ -9305,28 +9305,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M98">
-        <v>5.988778480046323</v>
+        <v>6.051161589213473</v>
       </c>
       <c r="N98">
-        <v>7.314554853287012</v>
+        <v>7.252171744119861</v>
       </c>
       <c r="O98">
-        <v>2.194366455986104</v>
+        <v>2.175651523235958</v>
       </c>
       <c r="P98">
-        <v>5.120188397300908</v>
+        <v>5.076520220883904</v>
       </c>
       <c r="Q98">
-        <v>5.250188397300908</v>
+        <v>5.206520220883903</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.860288110134988</v>
+        <v>2.45492372675226</v>
       </c>
       <c r="T98">
-        <v>12.65141411436753</v>
+        <v>16.79747679229697</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.221376759494105</v>
+        <v>2.198475968159114</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1251159118025678</v>
+        <v>0.1248826991997361</v>
       </c>
       <c r="C99">
-        <v>38.95303982069173</v>
+        <v>38.47511359413384</v>
       </c>
       <c r="D99">
-        <v>117.013667646727</v>
+        <v>117.3587375833241</v>
       </c>
       <c r="E99">
-        <v>11.63101151053499</v>
+        <v>12.45400767368999</v>
       </c>
       <c r="F99">
-        <v>79.83062782603525</v>
+        <v>80.65362398919025</v>
       </c>
       <c r="G99">
         <v>1.77</v>
@@ -9387,28 +9387,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M99">
-        <v>6.051161589213473</v>
+        <v>6.113544698380622</v>
       </c>
       <c r="N99">
-        <v>7.252171744119861</v>
+        <v>7.189788634952713</v>
       </c>
       <c r="O99">
-        <v>2.175651523235958</v>
+        <v>2.156936590485814</v>
       </c>
       <c r="P99">
-        <v>5.076520220883904</v>
+        <v>5.0328520444669</v>
       </c>
       <c r="Q99">
-        <v>5.206520220883903</v>
+        <v>5.162852044466899</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.45492372675226</v>
+        <v>3.644194959986802</v>
       </c>
       <c r="T99">
-        <v>16.79747679229697</v>
+        <v>25.08960214815584</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.198475968159114</v>
+        <v>2.176042539912593</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1248826991997361</v>
+        <v>0.1246494865969044</v>
       </c>
       <c r="C100">
-        <v>38.47511359413384</v>
+        <v>37.99922858969532</v>
       </c>
       <c r="D100">
-        <v>117.3587375833241</v>
+        <v>117.7058487420406</v>
       </c>
       <c r="E100">
-        <v>12.45400767368999</v>
+        <v>13.277003836845</v>
       </c>
       <c r="F100">
-        <v>80.65362398919025</v>
+        <v>81.47662015234526</v>
       </c>
       <c r="G100">
         <v>1.77</v>
@@ -9469,28 +9469,28 @@
         <v>13.30333333333333</v>
       </c>
       <c r="M100">
-        <v>6.113544698380622</v>
+        <v>6.175927807547771</v>
       </c>
       <c r="N100">
-        <v>7.189788634952713</v>
+        <v>7.127405525785563</v>
       </c>
       <c r="O100">
-        <v>2.156936590485814</v>
+        <v>2.138221657735669</v>
       </c>
       <c r="P100">
-        <v>5.0328520444669</v>
+        <v>4.989183868049894</v>
       </c>
       <c r="Q100">
-        <v>5.162852044466899</v>
+        <v>5.119183868049894</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.644194959986802</v>
+        <v>7.21200865969043</v>
       </c>
       <c r="T100">
-        <v>25.08960214815584</v>
+        <v>49.96597821573245</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.176042539912593</v>
+        <v>2.154062312236708</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1246494865969044</v>
-      </c>
-      <c r="C101">
-        <v>37.99922858969532</v>
-      </c>
-      <c r="D101">
-        <v>117.7058487420406</v>
-      </c>
-      <c r="E101">
-        <v>13.277003836845</v>
-      </c>
-      <c r="F101">
-        <v>81.47662015234526</v>
-      </c>
-      <c r="G101">
-        <v>1.77</v>
-      </c>
-      <c r="H101">
-        <v>14.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>13.43333333333334</v>
-      </c>
-      <c r="K101">
-        <v>0.13</v>
-      </c>
-      <c r="L101">
-        <v>13.30333333333333</v>
-      </c>
-      <c r="M101">
-        <v>6.175927807547771</v>
-      </c>
-      <c r="N101">
-        <v>7.127405525785563</v>
-      </c>
-      <c r="O101">
-        <v>2.138221657735669</v>
-      </c>
-      <c r="P101">
-        <v>4.989183868049894</v>
-      </c>
-      <c r="Q101">
-        <v>5.119183868049894</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.21200865969043</v>
-      </c>
-      <c r="T101">
-        <v>49.96597821573245</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.154062312236708</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
